--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_beverage_soft.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.202</v>
+        <v>-0.111</v>
       </c>
       <c r="G2">
-        <v>-0.3333333333333333</v>
+        <v>-0.2778443113772455</v>
       </c>
       <c r="H2">
-        <v>-0.3333333333333333</v>
+        <v>-0.2778443113772455</v>
       </c>
       <c r="I2">
-        <v>-0.560763888888889</v>
+        <v>-0.295808383233533</v>
       </c>
       <c r="J2">
-        <v>-0.560763888888889</v>
+        <v>-0.295808383233533</v>
       </c>
       <c r="K2">
-        <v>-1.65</v>
+        <v>3.63</v>
       </c>
       <c r="L2">
-        <v>-0.2864583333333333</v>
+        <v>0.4347305389221557</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +624,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.28</v>
+        <v>74.5</v>
       </c>
       <c r="V2">
-        <v>0.07970204841713222</v>
+        <v>0.198507860378364</v>
       </c>
       <c r="W2">
-        <v>-0.2825342465753425</v>
+        <v>0.8422273781902553</v>
       </c>
       <c r="X2">
-        <v>0.05358965594209392</v>
+        <v>0.09302093965624869</v>
       </c>
       <c r="Y2">
-        <v>-0.3361239025174364</v>
+        <v>0.7492064385340066</v>
       </c>
       <c r="Z2">
-        <v>1.254901960784314</v>
+        <v>2.119289340101523</v>
       </c>
       <c r="AA2">
-        <v>-0.7037037037037037</v>
+        <v>-0.6269035532994925</v>
       </c>
       <c r="AB2">
-        <v>0.05004585618949519</v>
+        <v>0.09344997202225748</v>
       </c>
       <c r="AC2">
-        <v>-0.7537495598931989</v>
+        <v>-0.72035352532175</v>
       </c>
       <c r="AD2">
-        <v>6.01</v>
+        <v>2.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6.01</v>
+        <v>2.4</v>
       </c>
       <c r="AG2">
-        <v>1.73</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.1006531569251382</v>
+        <v>0.006354249404289118</v>
       </c>
       <c r="AI2">
-        <v>0.5846303501945526</v>
+        <v>0.02687569988801791</v>
       </c>
       <c r="AJ2">
-        <v>0.0312105358109327</v>
+        <v>-0.237796833773087</v>
       </c>
       <c r="AK2">
-        <v>0.2883333333333333</v>
+        <v>-4.871621621621617</v>
       </c>
       <c r="AL2">
-        <v>0.163</v>
+        <v>0.228</v>
       </c>
       <c r="AM2">
-        <v>0.099</v>
+        <v>-0.246</v>
       </c>
       <c r="AN2">
-        <v>-2.146428571428571</v>
+        <v>-1.194029850746269</v>
       </c>
       <c r="AO2">
-        <v>-19.8159509202454</v>
+        <v>-10.83333333333333</v>
       </c>
       <c r="AP2">
-        <v>-0.6178571428571428</v>
+        <v>35.87064676616915</v>
       </c>
       <c r="AQ2">
-        <v>-32.62626262626262</v>
+        <v>10.04065040650407</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.202</v>
+        <v>-0.111</v>
       </c>
       <c r="G3">
-        <v>-0.3333333333333333</v>
+        <v>-0.2778443113772455</v>
       </c>
       <c r="H3">
-        <v>-0.3333333333333333</v>
+        <v>-0.2778443113772455</v>
       </c>
       <c r="I3">
-        <v>-0.560763888888889</v>
+        <v>-0.295808383233533</v>
       </c>
       <c r="J3">
-        <v>-0.560763888888889</v>
+        <v>-0.295808383233533</v>
       </c>
       <c r="K3">
-        <v>-1.65</v>
+        <v>3.63</v>
       </c>
       <c r="L3">
-        <v>-0.2864583333333333</v>
+        <v>0.4347305389221557</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +743,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +752,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.28</v>
+        <v>74.5</v>
       </c>
       <c r="V3">
-        <v>0.07970204841713222</v>
+        <v>0.198507860378364</v>
       </c>
       <c r="W3">
-        <v>-0.2825342465753425</v>
+        <v>0.8422273781902553</v>
       </c>
       <c r="X3">
-        <v>0.05358965594209392</v>
+        <v>0.09302093965624869</v>
       </c>
       <c r="Y3">
-        <v>-0.3361239025174364</v>
+        <v>0.7492064385340066</v>
       </c>
       <c r="Z3">
-        <v>1.254901960784314</v>
+        <v>2.119289340101523</v>
       </c>
       <c r="AA3">
-        <v>-0.7037037037037037</v>
+        <v>-0.6269035532994925</v>
       </c>
       <c r="AB3">
-        <v>0.05004585618949519</v>
+        <v>0.09344997202225748</v>
       </c>
       <c r="AC3">
-        <v>-0.7537495598931989</v>
+        <v>-0.72035352532175</v>
       </c>
       <c r="AD3">
-        <v>6.01</v>
+        <v>2.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.01</v>
+        <v>2.4</v>
       </c>
       <c r="AG3">
-        <v>1.73</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.1006531569251382</v>
+        <v>0.006354249404289118</v>
       </c>
       <c r="AI3">
-        <v>0.5846303501945526</v>
+        <v>0.02687569988801791</v>
       </c>
       <c r="AJ3">
-        <v>0.0312105358109327</v>
+        <v>-0.237796833773087</v>
       </c>
       <c r="AK3">
-        <v>0.2883333333333333</v>
+        <v>-4.871621621621617</v>
       </c>
       <c r="AL3">
-        <v>0.163</v>
+        <v>0.228</v>
       </c>
       <c r="AM3">
-        <v>0.099</v>
+        <v>-0.246</v>
       </c>
       <c r="AN3">
-        <v>-2.146428571428571</v>
+        <v>-1.194029850746269</v>
       </c>
       <c r="AO3">
-        <v>-19.8159509202454</v>
+        <v>-10.83333333333333</v>
       </c>
       <c r="AP3">
-        <v>-0.6178571428571428</v>
+        <v>35.87064676616915</v>
       </c>
       <c r="AQ3">
-        <v>-32.62626262626262</v>
+        <v>10.04065040650407</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_beverage_soft.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.111</v>
+        <v>-0.0269</v>
       </c>
       <c r="G2">
-        <v>-0.2778443113772455</v>
+        <v>-0.08524590163934427</v>
       </c>
       <c r="H2">
-        <v>-0.2778443113772455</v>
+        <v>-0.08524590163934427</v>
       </c>
       <c r="I2">
-        <v>-0.295808383233533</v>
+        <v>-0.05204918032786886</v>
       </c>
       <c r="J2">
-        <v>-0.295808383233533</v>
+        <v>-0.05204918032786886</v>
       </c>
       <c r="K2">
-        <v>3.63</v>
+        <v>4.87</v>
       </c>
       <c r="L2">
-        <v>0.4347305389221557</v>
+        <v>0.3991803278688525</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>74.5</v>
+        <v>63.8</v>
       </c>
       <c r="V2">
-        <v>0.198507860378364</v>
+        <v>0.2441637964026024</v>
       </c>
       <c r="W2">
-        <v>0.8422273781902553</v>
+        <v>0.05604142692750287</v>
       </c>
       <c r="X2">
-        <v>0.09302093965624869</v>
+        <v>0.07395887136790241</v>
       </c>
       <c r="Y2">
-        <v>0.7492064385340066</v>
+        <v>-0.01791744444039954</v>
       </c>
       <c r="Z2">
-        <v>2.119289340101523</v>
+        <v>0.8243243243243237</v>
       </c>
       <c r="AA2">
-        <v>-0.6269035532994925</v>
+        <v>-0.04290540540540537</v>
       </c>
       <c r="AB2">
-        <v>0.09344997202225748</v>
+        <v>0.07369564964994903</v>
       </c>
       <c r="AC2">
-        <v>-0.72035352532175</v>
+        <v>-0.1166010550553544</v>
       </c>
       <c r="AD2">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AG2">
-        <v>-72.09999999999999</v>
+        <v>-61.47</v>
       </c>
       <c r="AH2">
-        <v>0.006354249404289118</v>
+        <v>0.00883814436900201</v>
       </c>
       <c r="AI2">
-        <v>0.02687569988801791</v>
+        <v>0.02475300116859662</v>
       </c>
       <c r="AJ2">
-        <v>-0.237796833773087</v>
+        <v>-0.3076114697492869</v>
       </c>
       <c r="AK2">
-        <v>-4.871621621621617</v>
+        <v>-2.026706231454006</v>
       </c>
       <c r="AL2">
-        <v>0.228</v>
+        <v>0.04</v>
       </c>
       <c r="AM2">
-        <v>-0.246</v>
+        <v>-2.55</v>
       </c>
       <c r="AN2">
-        <v>-1.194029850746269</v>
+        <v>77.66666666666667</v>
       </c>
       <c r="AO2">
-        <v>-10.83333333333333</v>
+        <v>-15.875</v>
       </c>
       <c r="AP2">
-        <v>35.87064676616915</v>
+        <v>-2049</v>
       </c>
       <c r="AQ2">
-        <v>10.04065040650407</v>
+        <v>0.2490196078431373</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Emirates Refreshments (P.S.C.) (DFM:ERC)</t>
+          <t>Emirates Reem Investments Company PJSC (DFM:ERC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.111</v>
+        <v>-0.0269</v>
       </c>
       <c r="G3">
-        <v>-0.2778443113772455</v>
+        <v>-0.08524590163934427</v>
       </c>
       <c r="H3">
-        <v>-0.2778443113772455</v>
+        <v>-0.08524590163934427</v>
       </c>
       <c r="I3">
-        <v>-0.295808383233533</v>
+        <v>-0.05204918032786886</v>
       </c>
       <c r="J3">
-        <v>-0.295808383233533</v>
+        <v>-0.05204918032786886</v>
       </c>
       <c r="K3">
-        <v>3.63</v>
+        <v>4.87</v>
       </c>
       <c r="L3">
-        <v>0.4347305389221557</v>
+        <v>0.3991803278688525</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>74.5</v>
+        <v>63.8</v>
       </c>
       <c r="V3">
-        <v>0.198507860378364</v>
+        <v>0.2441637964026024</v>
       </c>
       <c r="W3">
-        <v>0.8422273781902553</v>
+        <v>0.05604142692750287</v>
       </c>
       <c r="X3">
-        <v>0.09302093965624869</v>
+        <v>0.07395887136790241</v>
       </c>
       <c r="Y3">
-        <v>0.7492064385340066</v>
+        <v>-0.01791744444039954</v>
       </c>
       <c r="Z3">
-        <v>2.119289340101523</v>
+        <v>0.8243243243243237</v>
       </c>
       <c r="AA3">
-        <v>-0.6269035532994925</v>
+        <v>-0.04290540540540537</v>
       </c>
       <c r="AB3">
-        <v>0.09344997202225748</v>
+        <v>0.07369564964994903</v>
       </c>
       <c r="AC3">
-        <v>-0.72035352532175</v>
+        <v>-0.1166010550553544</v>
       </c>
       <c r="AD3">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AG3">
-        <v>-72.09999999999999</v>
+        <v>-61.47</v>
       </c>
       <c r="AH3">
-        <v>0.006354249404289118</v>
+        <v>0.00883814436900201</v>
       </c>
       <c r="AI3">
-        <v>0.02687569988801791</v>
+        <v>0.02475300116859662</v>
       </c>
       <c r="AJ3">
-        <v>-0.237796833773087</v>
+        <v>-0.3076114697492869</v>
       </c>
       <c r="AK3">
-        <v>-4.871621621621617</v>
+        <v>-2.026706231454006</v>
       </c>
       <c r="AL3">
-        <v>0.228</v>
+        <v>0.04</v>
       </c>
       <c r="AM3">
-        <v>-0.246</v>
+        <v>-2.55</v>
       </c>
       <c r="AN3">
-        <v>-1.194029850746269</v>
+        <v>77.66666666666667</v>
       </c>
       <c r="AO3">
-        <v>-10.83333333333333</v>
+        <v>-15.875</v>
       </c>
       <c r="AP3">
-        <v>35.87064676616915</v>
+        <v>-2049</v>
       </c>
       <c r="AQ3">
-        <v>10.04065040650407</v>
+        <v>0.2490196078431373</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_beverage_soft.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07854104614555765</v>
+        <v>0.07837844353019376</v>
       </c>
       <c r="C2">
-        <v>232.5983640787131</v>
+        <v>231.1022749423134</v>
       </c>
       <c r="D2">
-        <v>166.5983640787131</v>
+        <v>167.4298749423134</v>
       </c>
       <c r="E2">
-        <v>-1.06</v>
+        <v>1.2676</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.3276</v>
       </c>
       <c r="G2">
         <v>66</v>
@@ -1439,28 +1439,28 @@
         <v>2.17</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.11707828</v>
       </c>
       <c r="N2">
-        <v>2.17</v>
+        <v>2.05292172</v>
       </c>
       <c r="O2">
-        <v>0.5425</v>
+        <v>0.51323043</v>
       </c>
       <c r="P2">
-        <v>1.6275</v>
+        <v>1.53969129</v>
       </c>
       <c r="Q2">
-        <v>2.7675</v>
+        <v>2.67969129</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07854104614555765</v>
+        <v>0.07878908437393309</v>
       </c>
       <c r="T2">
-        <v>0.6562503962404382</v>
+        <v>0.6612219901513506</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>18.5346077854919</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07837844353019376</v>
+        <v>0.07826384091482987</v>
       </c>
       <c r="C3">
-        <v>231.1022749423134</v>
+        <v>229.3657295131136</v>
       </c>
       <c r="D3">
-        <v>167.4298749423134</v>
+        <v>168.0209295131136</v>
       </c>
       <c r="E3">
-        <v>1.2676</v>
+        <v>3.5952</v>
       </c>
       <c r="F3">
-        <v>2.3276</v>
+        <v>4.6552</v>
       </c>
       <c r="G3">
         <v>66</v>
@@ -1521,45 +1521,45 @@
         <v>2.17</v>
       </c>
       <c r="M3">
-        <v>0.11707828</v>
+        <v>0.2490532</v>
       </c>
       <c r="N3">
-        <v>2.05292172</v>
+        <v>1.9209468</v>
       </c>
       <c r="O3">
-        <v>0.51323043</v>
+        <v>0.4802367</v>
       </c>
       <c r="P3">
-        <v>1.53969129</v>
+        <v>1.4407101</v>
       </c>
       <c r="Q3">
-        <v>2.67969129</v>
+        <v>2.5807101</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07878908437393309</v>
+        <v>0.07904218460696925</v>
       </c>
       <c r="T3">
-        <v>0.6612219901513506</v>
+        <v>0.6662950451624858</v>
       </c>
       <c r="U3">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.03772499999999999</v>
+        <v>0.040125</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y3">
-        <v>18.5346077854919</v>
+        <v>8.712997865516282</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07826384091482987</v>
+        <v>0.07816573829946598</v>
       </c>
       <c r="C4">
-        <v>229.3657295131136</v>
+        <v>227.5474116579729</v>
       </c>
       <c r="D4">
-        <v>168.0209295131136</v>
+        <v>168.5302116579729</v>
       </c>
       <c r="E4">
-        <v>3.5952</v>
+        <v>5.922799999999999</v>
       </c>
       <c r="F4">
-        <v>4.6552</v>
+        <v>6.982799999999999</v>
       </c>
       <c r="G4">
         <v>66</v>
@@ -1603,45 +1603,45 @@
         <v>2.17</v>
       </c>
       <c r="M4">
-        <v>0.2490532</v>
+        <v>0.38614884</v>
       </c>
       <c r="N4">
-        <v>1.9209468</v>
+        <v>1.78385116</v>
       </c>
       <c r="O4">
-        <v>0.4802367</v>
+        <v>0.44596279</v>
       </c>
       <c r="P4">
-        <v>1.4407101</v>
+        <v>1.33788837</v>
       </c>
       <c r="Q4">
-        <v>2.5807101</v>
+        <v>2.47788837</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07904218460696925</v>
+        <v>0.07930050340151132</v>
       </c>
       <c r="T4">
-        <v>0.6662950451624858</v>
+        <v>0.6714726992460154</v>
       </c>
       <c r="U4">
-        <v>0.0535</v>
+        <v>0.0553</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.040125</v>
+        <v>0.041475</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y4">
-        <v>8.712997865516282</v>
+        <v>5.619594765583137</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07816573829946598</v>
+        <v>0.07811563568410207</v>
       </c>
       <c r="C5">
-        <v>227.5474116579729</v>
+        <v>225.4811032647492</v>
       </c>
       <c r="D5">
-        <v>168.5302116579729</v>
+        <v>168.7915032647492</v>
       </c>
       <c r="E5">
-        <v>5.922799999999999</v>
+        <v>8.250399999999999</v>
       </c>
       <c r="F5">
-        <v>6.982799999999999</v>
+        <v>9.3104</v>
       </c>
       <c r="G5">
         <v>66</v>
@@ -1685,45 +1685,45 @@
         <v>2.17</v>
       </c>
       <c r="M5">
-        <v>0.38614884</v>
+        <v>0.53814112</v>
       </c>
       <c r="N5">
-        <v>1.78385116</v>
+        <v>1.63185888</v>
       </c>
       <c r="O5">
-        <v>0.44596279</v>
+        <v>0.4079647199999999</v>
       </c>
       <c r="P5">
-        <v>1.33788837</v>
+        <v>1.22389416</v>
       </c>
       <c r="Q5">
-        <v>2.47788837</v>
+        <v>2.36389416</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07930050340151132</v>
+        <v>0.07956420383760633</v>
       </c>
       <c r="T5">
-        <v>0.6714726992460154</v>
+        <v>0.6767582211229519</v>
       </c>
       <c r="U5">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y5">
-        <v>5.619594765583137</v>
+        <v>4.032399531186169</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07811563568410207</v>
+        <v>0.07853803306873818</v>
       </c>
       <c r="C6">
-        <v>225.4811032647492</v>
+        <v>220.9756971217189</v>
       </c>
       <c r="D6">
-        <v>168.7915032647492</v>
+        <v>166.6136971217189</v>
       </c>
       <c r="E6">
-        <v>8.250399999999999</v>
+        <v>10.578</v>
       </c>
       <c r="F6">
-        <v>9.3104</v>
+        <v>11.638</v>
       </c>
       <c r="G6">
         <v>66</v>
@@ -1767,45 +1767,45 @@
         <v>2.17</v>
       </c>
       <c r="M6">
-        <v>0.53814112</v>
+        <v>0.8367722000000001</v>
       </c>
       <c r="N6">
-        <v>1.63185888</v>
+        <v>1.3332278</v>
       </c>
       <c r="O6">
-        <v>0.4079647199999999</v>
+        <v>0.33330695</v>
       </c>
       <c r="P6">
-        <v>1.22389416</v>
+        <v>0.99992085</v>
       </c>
       <c r="Q6">
-        <v>2.36389416</v>
+        <v>2.13992085</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07956420383760633</v>
+        <v>0.07983345586182966</v>
       </c>
       <c r="T6">
-        <v>0.6767582211229519</v>
+        <v>0.6821550171446661</v>
       </c>
       <c r="U6">
-        <v>0.0578</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.04335</v>
+        <v>0.053925</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>4.032399531186169</v>
+        <v>2.593298391127238</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07853803306873818</v>
+        <v>0.07871293045337428</v>
       </c>
       <c r="C7">
-        <v>220.9756971217189</v>
+        <v>217.7627216941974</v>
       </c>
       <c r="D7">
-        <v>166.6136971217189</v>
+        <v>165.7283216941974</v>
       </c>
       <c r="E7">
-        <v>10.578</v>
+        <v>12.9056</v>
       </c>
       <c r="F7">
-        <v>11.638</v>
+        <v>13.9656</v>
       </c>
       <c r="G7">
         <v>66</v>
@@ -1849,45 +1849,45 @@
         <v>2.17</v>
       </c>
       <c r="M7">
-        <v>0.8367722000000001</v>
+        <v>1.05859248</v>
       </c>
       <c r="N7">
-        <v>1.3332278</v>
+        <v>1.11140752</v>
       </c>
       <c r="O7">
-        <v>0.33330695</v>
+        <v>0.2778518799999999</v>
       </c>
       <c r="P7">
-        <v>0.99992085</v>
+        <v>0.8335556399999998</v>
       </c>
       <c r="Q7">
-        <v>2.13992085</v>
+        <v>1.97355564</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07983345586182966</v>
+        <v>0.08010843665252584</v>
       </c>
       <c r="T7">
-        <v>0.6821550171446661</v>
+        <v>0.6876666386136507</v>
       </c>
       <c r="U7">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y7">
-        <v>2.593298391127238</v>
+        <v>2.049891758157965</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07871293045337428</v>
+        <v>0.08276049334503395</v>
       </c>
       <c r="C8">
-        <v>217.7627216941974</v>
+        <v>197.2861268005295</v>
       </c>
       <c r="D8">
-        <v>165.7283216941974</v>
+        <v>147.5793268005295</v>
       </c>
       <c r="E8">
-        <v>12.9056</v>
+        <v>15.2332</v>
       </c>
       <c r="F8">
-        <v>13.9656</v>
+        <v>16.2932</v>
       </c>
       <c r="G8">
         <v>66</v>
@@ -1931,45 +1931,45 @@
         <v>2.17</v>
       </c>
       <c r="M8">
-        <v>1.05859248</v>
+        <v>2.39184176</v>
       </c>
       <c r="N8">
-        <v>1.11140752</v>
+        <v>-0.2218417600000002</v>
       </c>
       <c r="O8">
-        <v>0.27785188</v>
+        <v>-0.05546044000000006</v>
       </c>
       <c r="P8">
-        <v>0.8335556399999999</v>
+        <v>-0.1663813200000002</v>
       </c>
       <c r="Q8">
-        <v>1.97355564</v>
+        <v>0.97361868</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08010843665252584</v>
+        <v>0.08044647341296726</v>
       </c>
       <c r="T8">
-        <v>0.6876666386136507</v>
+        <v>0.6944421324997437</v>
       </c>
       <c r="U8">
-        <v>0.07580000000000001</v>
+        <v>0.1468</v>
       </c>
       <c r="V8">
-        <v>0.25</v>
+        <v>0.2268126633929161</v>
       </c>
       <c r="W8">
-        <v>0.05685</v>
+        <v>0.1135039010139199</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y8">
-        <v>2.049891758157965</v>
+        <v>0.9072506535716642</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08276049334503395</v>
+        <v>0.08823028715509817</v>
       </c>
       <c r="C9">
-        <v>197.2861268005295</v>
+        <v>175.9337088614883</v>
       </c>
       <c r="D9">
-        <v>147.5793268005295</v>
+        <v>128.5545088614883</v>
       </c>
       <c r="E9">
-        <v>15.2332</v>
+        <v>17.5608</v>
       </c>
       <c r="F9">
-        <v>16.2932</v>
+        <v>18.6208</v>
       </c>
       <c r="G9">
         <v>66</v>
@@ -2013,45 +2013,45 @@
         <v>2.17</v>
       </c>
       <c r="M9">
-        <v>2.391841760000001</v>
+        <v>3.73905664</v>
       </c>
       <c r="N9">
-        <v>-0.2218417600000007</v>
+        <v>-1.56905664</v>
       </c>
       <c r="O9">
-        <v>-0.05546044000000017</v>
+        <v>-0.39226416</v>
       </c>
       <c r="P9">
-        <v>-0.1663813200000005</v>
+        <v>-1.17679248</v>
       </c>
       <c r="Q9">
-        <v>0.9736186799999996</v>
+        <v>-0.03679247999999991</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08044647341296726</v>
+        <v>0.08097501530883019</v>
       </c>
       <c r="T9">
-        <v>0.6944421324997437</v>
+        <v>0.7050360465441423</v>
       </c>
       <c r="U9">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V9">
-        <v>0.226812663392916</v>
+        <v>0.1450900727730083</v>
       </c>
       <c r="W9">
-        <v>0.1135039010139199</v>
+        <v>0.1716659133871799</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y9">
-        <v>0.9072506535716641</v>
+        <v>0.5803602910920334</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08823028715509817</v>
+        <v>0.08978028715509818</v>
       </c>
       <c r="C10">
-        <v>175.9337088614883</v>
+        <v>169.0754542972602</v>
       </c>
       <c r="D10">
-        <v>128.5545088614883</v>
+        <v>124.0238542972602</v>
       </c>
       <c r="E10">
-        <v>17.5608</v>
+        <v>19.8884</v>
       </c>
       <c r="F10">
-        <v>18.6208</v>
+        <v>20.9484</v>
       </c>
       <c r="G10">
         <v>66</v>
@@ -2095,37 +2095,37 @@
         <v>2.17</v>
       </c>
       <c r="M10">
-        <v>3.73905664</v>
+        <v>4.20643872</v>
       </c>
       <c r="N10">
-        <v>-1.56905664</v>
+        <v>-2.03643872</v>
       </c>
       <c r="O10">
-        <v>-0.39226416</v>
+        <v>-0.5091096800000001</v>
       </c>
       <c r="P10">
-        <v>-1.17679248</v>
+        <v>-1.52732904</v>
       </c>
       <c r="Q10">
-        <v>-0.03679247999999991</v>
+        <v>-0.3873290400000002</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08097501530883019</v>
+        <v>0.08136155393859756</v>
       </c>
       <c r="T10">
-        <v>0.7050360465441423</v>
+        <v>0.7127836954072648</v>
       </c>
       <c r="U10">
         <v>0.2008</v>
       </c>
       <c r="V10">
-        <v>0.1450900727730083</v>
+        <v>0.1289689535760074</v>
       </c>
       <c r="W10">
-        <v>0.1716659133871799</v>
+        <v>0.1749030341219377</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.5803602910920334</v>
+        <v>0.5158758143040296</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08978028715509818</v>
+        <v>0.09488669564598108</v>
       </c>
       <c r="C11">
-        <v>169.0754542972602</v>
+        <v>153.8458560201078</v>
       </c>
       <c r="D11">
-        <v>124.0238542972602</v>
+        <v>111.1218560201078</v>
       </c>
       <c r="E11">
-        <v>19.8884</v>
+        <v>22.216</v>
       </c>
       <c r="F11">
-        <v>20.9484</v>
+        <v>23.276</v>
       </c>
       <c r="G11">
         <v>66</v>
@@ -2177,45 +2177,45 @@
         <v>2.17</v>
       </c>
       <c r="M11">
-        <v>4.20643872</v>
+        <v>5.4884808</v>
       </c>
       <c r="N11">
-        <v>-2.03643872</v>
+        <v>-3.3184808</v>
       </c>
       <c r="O11">
-        <v>-0.5091096800000001</v>
+        <v>-0.8296201999999999</v>
       </c>
       <c r="P11">
-        <v>-1.52732904</v>
+        <v>-2.4888606</v>
       </c>
       <c r="Q11">
-        <v>-0.3873290400000002</v>
+        <v>-1.3488606</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08136155393859756</v>
+        <v>0.08181935841667409</v>
       </c>
       <c r="T11">
-        <v>0.7127836954072648</v>
+        <v>0.7219597727018849</v>
       </c>
       <c r="U11">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.1289689535760074</v>
+        <v>0.09884338121397819</v>
       </c>
       <c r="W11">
-        <v>0.1749030341219377</v>
+        <v>0.2124927307097439</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y11">
-        <v>0.5158758143040296</v>
+        <v>0.3953735248559128</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09488669564598108</v>
+        <v>0.09678669564598107</v>
       </c>
       <c r="C12">
-        <v>153.8458560201078</v>
+        <v>147.377341929417</v>
       </c>
       <c r="D12">
-        <v>111.1218560201078</v>
+        <v>106.980941929417</v>
       </c>
       <c r="E12">
-        <v>22.216</v>
+        <v>24.5436</v>
       </c>
       <c r="F12">
-        <v>23.276</v>
+        <v>25.6036</v>
       </c>
       <c r="G12">
         <v>66</v>
@@ -2259,37 +2259,37 @@
         <v>2.17</v>
       </c>
       <c r="M12">
-        <v>5.4884808</v>
+        <v>6.03732888</v>
       </c>
       <c r="N12">
-        <v>-3.318480800000001</v>
+        <v>-3.867328880000001</v>
       </c>
       <c r="O12">
-        <v>-0.8296202000000001</v>
+        <v>-0.9668322200000001</v>
       </c>
       <c r="P12">
-        <v>-2.488860600000001</v>
+        <v>-2.90049666</v>
       </c>
       <c r="Q12">
-        <v>-1.348860600000001</v>
+        <v>-1.76049666</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08181935841667409</v>
+        <v>0.08222407030899626</v>
       </c>
       <c r="T12">
-        <v>0.7219597727018849</v>
+        <v>0.7300716802603331</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.09884338121397818</v>
+        <v>0.08985761928543472</v>
       </c>
       <c r="W12">
-        <v>0.2124927307097439</v>
+        <v>0.2146115733724945</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.3953735248559127</v>
+        <v>0.3594304771417388</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09678669564598107</v>
+        <v>0.09868669564598107</v>
       </c>
       <c r="C13">
-        <v>147.377341929417</v>
+        <v>141.2063596348127</v>
       </c>
       <c r="D13">
-        <v>106.980941929417</v>
+        <v>103.1375596348127</v>
       </c>
       <c r="E13">
-        <v>24.5436</v>
+        <v>26.8712</v>
       </c>
       <c r="F13">
-        <v>25.6036</v>
+        <v>27.9312</v>
       </c>
       <c r="G13">
         <v>66</v>
@@ -2341,37 +2341,37 @@
         <v>2.17</v>
       </c>
       <c r="M13">
-        <v>6.03732888</v>
+        <v>6.58617696</v>
       </c>
       <c r="N13">
-        <v>-3.867328880000001</v>
+        <v>-4.41617696</v>
       </c>
       <c r="O13">
-        <v>-0.9668322200000001</v>
+        <v>-1.10404424</v>
       </c>
       <c r="P13">
-        <v>-2.90049666</v>
+        <v>-3.31213272</v>
       </c>
       <c r="Q13">
-        <v>-1.76049666</v>
+        <v>-2.17213272</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08222407030899626</v>
+        <v>0.08263798019887122</v>
       </c>
       <c r="T13">
-        <v>0.7300716802603331</v>
+        <v>0.7383679493542005</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.08985761928543472</v>
+        <v>0.08236948434498183</v>
       </c>
       <c r="W13">
-        <v>0.2146115733724945</v>
+        <v>0.2163772755914533</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.3594304771417388</v>
+        <v>0.3294779373799274</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09868669564598107</v>
+        <v>0.1005866956459811</v>
       </c>
       <c r="C14">
-        <v>141.2063596348127</v>
+        <v>135.3019539706711</v>
       </c>
       <c r="D14">
-        <v>103.1375596348127</v>
+        <v>99.56075397067109</v>
       </c>
       <c r="E14">
-        <v>26.8712</v>
+        <v>29.1988</v>
       </c>
       <c r="F14">
-        <v>27.9312</v>
+        <v>30.2588</v>
       </c>
       <c r="G14">
         <v>66</v>
@@ -2423,37 +2423,37 @@
         <v>2.17</v>
       </c>
       <c r="M14">
-        <v>6.58617696</v>
+        <v>7.13502504</v>
       </c>
       <c r="N14">
-        <v>-4.41617696</v>
+        <v>-4.96502504</v>
       </c>
       <c r="O14">
-        <v>-1.10404424</v>
+        <v>-1.24125626</v>
       </c>
       <c r="P14">
-        <v>-3.31213272</v>
+        <v>-3.72376878</v>
       </c>
       <c r="Q14">
-        <v>-2.17213272</v>
+        <v>-2.58376878</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08263798019887122</v>
+        <v>0.08306140525862837</v>
       </c>
       <c r="T14">
-        <v>0.7383679493542005</v>
+        <v>0.746854937277812</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.08236948434498183</v>
+        <v>0.0760333701645986</v>
       </c>
       <c r="W14">
-        <v>0.2163772755914533</v>
+        <v>0.2178713313151877</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.3294779373799274</v>
+        <v>0.3041334806583944</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1005866956459811</v>
+        <v>0.1024866956459811</v>
       </c>
       <c r="C15">
-        <v>135.3019539706711</v>
+        <v>129.6373199384593</v>
       </c>
       <c r="D15">
-        <v>99.56075397067109</v>
+        <v>96.22371993845925</v>
       </c>
       <c r="E15">
-        <v>29.1988</v>
+        <v>31.52640000000001</v>
       </c>
       <c r="F15">
-        <v>30.2588</v>
+        <v>32.5864</v>
       </c>
       <c r="G15">
         <v>66</v>
@@ -2505,37 +2505,37 @@
         <v>2.17</v>
       </c>
       <c r="M15">
-        <v>7.13502504</v>
+        <v>7.683873120000001</v>
       </c>
       <c r="N15">
-        <v>-4.96502504</v>
+        <v>-5.513873120000001</v>
       </c>
       <c r="O15">
-        <v>-1.24125626</v>
+        <v>-1.37846828</v>
       </c>
       <c r="P15">
-        <v>-3.72376878</v>
+        <v>-4.135404840000001</v>
       </c>
       <c r="Q15">
-        <v>-2.58376878</v>
+        <v>-2.995404840000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08306140525862837</v>
+        <v>0.08349467741279847</v>
       </c>
       <c r="T15">
-        <v>0.746854937277812</v>
+        <v>0.7555392970136006</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.0760333701645986</v>
+        <v>0.07060241515284155</v>
       </c>
       <c r="W15">
-        <v>0.2178713313151877</v>
+        <v>0.21915195050696</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.3041334806583944</v>
+        <v>0.2824096606113662</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1024866956459811</v>
+        <v>0.1043866956459811</v>
       </c>
       <c r="C16">
-        <v>129.6373199384593</v>
+        <v>124.1891297452894</v>
       </c>
       <c r="D16">
-        <v>96.22371993845925</v>
+        <v>93.10312974528945</v>
       </c>
       <c r="E16">
-        <v>31.52640000000001</v>
+        <v>33.854</v>
       </c>
       <c r="F16">
-        <v>32.5864</v>
+        <v>34.914</v>
       </c>
       <c r="G16">
         <v>66</v>
@@ -2587,37 +2587,37 @@
         <v>2.17</v>
       </c>
       <c r="M16">
-        <v>7.683873120000001</v>
+        <v>8.2327212</v>
       </c>
       <c r="N16">
-        <v>-5.513873120000001</v>
+        <v>-6.0627212</v>
       </c>
       <c r="O16">
-        <v>-1.37846828</v>
+        <v>-1.5156803</v>
       </c>
       <c r="P16">
-        <v>-4.135404840000001</v>
+        <v>-4.547040900000001</v>
       </c>
       <c r="Q16">
-        <v>-2.995404840000001</v>
+        <v>-3.407040900000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08349467741279847</v>
+        <v>0.08393814420589021</v>
       </c>
       <c r="T16">
-        <v>0.7555392970136006</v>
+        <v>0.7644279946255252</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.07060241515284155</v>
+        <v>0.06589558747598545</v>
       </c>
       <c r="W16">
-        <v>0.21915195050696</v>
+        <v>0.2202618204731626</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.2824096606113662</v>
+        <v>0.2635823499039418</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1043866956459811</v>
+        <v>0.1062866956459811</v>
       </c>
       <c r="C17">
-        <v>124.1891297452894</v>
+        <v>118.9369866763245</v>
       </c>
       <c r="D17">
-        <v>93.10312974528945</v>
+        <v>90.17858667632446</v>
       </c>
       <c r="E17">
-        <v>33.85399999999999</v>
+        <v>36.1816</v>
       </c>
       <c r="F17">
-        <v>34.91399999999999</v>
+        <v>37.2416</v>
       </c>
       <c r="G17">
         <v>66</v>
@@ -2669,37 +2669,37 @@
         <v>2.17</v>
       </c>
       <c r="M17">
-        <v>8.232721199999999</v>
+        <v>8.781569279999999</v>
       </c>
       <c r="N17">
-        <v>-6.062721199999999</v>
+        <v>-6.611569279999999</v>
       </c>
       <c r="O17">
-        <v>-1.5156803</v>
+        <v>-1.65289232</v>
       </c>
       <c r="P17">
-        <v>-4.547040899999999</v>
+        <v>-4.95867696</v>
       </c>
       <c r="Q17">
-        <v>-3.407040899999999</v>
+        <v>-3.81867696</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08393814420589021</v>
+        <v>0.0843921697321508</v>
       </c>
       <c r="T17">
-        <v>0.7644279946255252</v>
+        <v>0.7735283278948767</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.06589558747598546</v>
+        <v>0.06177711325873637</v>
       </c>
       <c r="W17">
-        <v>0.2202618204731626</v>
+        <v>0.22123295669359</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.2635823499039419</v>
+        <v>0.2471084530349454</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1062866956459811</v>
+        <v>0.1081866956459811</v>
       </c>
       <c r="C18">
-        <v>118.9369866763245</v>
+        <v>113.8629787617701</v>
       </c>
       <c r="D18">
-        <v>90.17858667632446</v>
+        <v>87.43217876177009</v>
       </c>
       <c r="E18">
-        <v>36.1816</v>
+        <v>38.5092</v>
       </c>
       <c r="F18">
-        <v>37.2416</v>
+        <v>39.5692</v>
       </c>
       <c r="G18">
         <v>66</v>
@@ -2751,37 +2751,37 @@
         <v>2.17</v>
       </c>
       <c r="M18">
-        <v>8.781569279999999</v>
+        <v>9.33041736</v>
       </c>
       <c r="N18">
-        <v>-6.611569279999999</v>
+        <v>-7.16041736</v>
       </c>
       <c r="O18">
-        <v>-1.65289232</v>
+        <v>-1.79010434</v>
       </c>
       <c r="P18">
-        <v>-4.95867696</v>
+        <v>-5.37031302</v>
       </c>
       <c r="Q18">
-        <v>-3.81867696</v>
+        <v>-4.230313020000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0843921697321508</v>
+        <v>0.08485713563253816</v>
       </c>
       <c r="T18">
-        <v>0.7735283278948767</v>
+        <v>0.7828479463032487</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.06177711325873637</v>
+        <v>0.05814316541998717</v>
       </c>
       <c r="W18">
-        <v>0.22123295669359</v>
+        <v>0.222089841593967</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.2471084530349454</v>
+        <v>0.2325726616799487</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1081866956459811</v>
+        <v>0.1100866956459811</v>
       </c>
       <c r="C19">
-        <v>113.8629787617701</v>
+        <v>108.9513115923798</v>
       </c>
       <c r="D19">
-        <v>87.43217876177009</v>
+        <v>84.84811159237985</v>
       </c>
       <c r="E19">
-        <v>38.5092</v>
+        <v>40.8368</v>
       </c>
       <c r="F19">
-        <v>39.5692</v>
+        <v>41.89680000000001</v>
       </c>
       <c r="G19">
         <v>66</v>
@@ -2833,37 +2833,37 @@
         <v>2.17</v>
       </c>
       <c r="M19">
-        <v>9.33041736</v>
+        <v>9.879265440000001</v>
       </c>
       <c r="N19">
-        <v>-7.16041736</v>
+        <v>-7.709265440000001</v>
       </c>
       <c r="O19">
-        <v>-1.79010434</v>
+        <v>-1.92731636</v>
       </c>
       <c r="P19">
-        <v>-5.37031302</v>
+        <v>-5.78194908</v>
       </c>
       <c r="Q19">
-        <v>-4.230313020000001</v>
+        <v>-4.64194908</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08485713563253816</v>
+        <v>0.08533344216464228</v>
       </c>
       <c r="T19">
-        <v>0.7828479463032487</v>
+        <v>0.7923948724776786</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.05814316541998717</v>
+        <v>0.05491298956332121</v>
       </c>
       <c r="W19">
-        <v>0.222089841593967</v>
+        <v>0.2228515170609689</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.2325726616799487</v>
+        <v>0.2196519582532849</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1100866956459811</v>
+        <v>0.1119866956459811</v>
       </c>
       <c r="C20">
-        <v>108.9513115923798</v>
+        <v>104.1880043788364</v>
       </c>
       <c r="D20">
-        <v>84.84811159237985</v>
+        <v>82.41240437883637</v>
       </c>
       <c r="E20">
-        <v>40.8368</v>
+        <v>43.16439999999999</v>
       </c>
       <c r="F20">
-        <v>41.8968</v>
+        <v>44.2244</v>
       </c>
       <c r="G20">
         <v>66</v>
@@ -2915,37 +2915,37 @@
         <v>2.17</v>
       </c>
       <c r="M20">
-        <v>9.879265439999999</v>
+        <v>10.42811352</v>
       </c>
       <c r="N20">
-        <v>-7.709265439999999</v>
+        <v>-8.25811352</v>
       </c>
       <c r="O20">
-        <v>-1.92731636</v>
+        <v>-2.06452838</v>
       </c>
       <c r="P20">
-        <v>-5.78194908</v>
+        <v>-6.19358514</v>
       </c>
       <c r="Q20">
-        <v>-4.64194908</v>
+        <v>-5.053585139999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08533344216464228</v>
+        <v>0.08582150935186009</v>
       </c>
       <c r="T20">
-        <v>0.7923948724776786</v>
+        <v>0.8021775252243166</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.05491298956332122</v>
+        <v>0.05202283221788326</v>
       </c>
       <c r="W20">
-        <v>0.2228515170609689</v>
+        <v>0.2235330161630231</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.2196519582532849</v>
+        <v>0.208091328871533</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1119866956459811</v>
+        <v>0.1138866956459811</v>
       </c>
       <c r="C21">
-        <v>104.1880043788364</v>
+        <v>99.56063690100268</v>
       </c>
       <c r="D21">
-        <v>82.41240437883637</v>
+        <v>80.11263690100267</v>
       </c>
       <c r="E21">
-        <v>43.16439999999999</v>
+        <v>45.492</v>
       </c>
       <c r="F21">
-        <v>44.2244</v>
+        <v>46.552</v>
       </c>
       <c r="G21">
         <v>66</v>
@@ -2997,37 +2997,37 @@
         <v>2.17</v>
       </c>
       <c r="M21">
-        <v>10.42811352</v>
+        <v>10.9769616</v>
       </c>
       <c r="N21">
-        <v>-8.25811352</v>
+        <v>-8.806961600000001</v>
       </c>
       <c r="O21">
-        <v>-2.06452838</v>
+        <v>-2.2017404</v>
       </c>
       <c r="P21">
-        <v>-6.19358514</v>
+        <v>-6.605221200000001</v>
       </c>
       <c r="Q21">
-        <v>-5.053585139999999</v>
+        <v>-5.4652212</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08582150935186009</v>
+        <v>0.08632177821875833</v>
       </c>
       <c r="T21">
-        <v>0.8021775252243166</v>
+        <v>0.8122047442896205</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.05202283221788326</v>
+        <v>0.04942169060698909</v>
       </c>
       <c r="W21">
-        <v>0.2235330161630231</v>
+        <v>0.224146365354872</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.208091328871533</v>
+        <v>0.1976867624279564</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1138866956459811</v>
+        <v>0.1157866956459811</v>
       </c>
       <c r="C22">
-        <v>99.56063690100268</v>
+        <v>95.05813767612909</v>
       </c>
       <c r="D22">
-        <v>80.11263690100267</v>
+        <v>77.9377376761291</v>
       </c>
       <c r="E22">
-        <v>45.492</v>
+        <v>47.8196</v>
       </c>
       <c r="F22">
-        <v>46.552</v>
+        <v>48.8796</v>
       </c>
       <c r="G22">
         <v>66</v>
@@ -3079,37 +3079,37 @@
         <v>2.17</v>
       </c>
       <c r="M22">
-        <v>10.9769616</v>
+        <v>11.52580968</v>
       </c>
       <c r="N22">
-        <v>-8.806961600000001</v>
+        <v>-9.355809680000002</v>
       </c>
       <c r="O22">
-        <v>-2.2017404</v>
+        <v>-2.33895242</v>
       </c>
       <c r="P22">
-        <v>-6.605221200000001</v>
+        <v>-7.016857260000002</v>
       </c>
       <c r="Q22">
-        <v>-5.4652212</v>
+        <v>-5.876857260000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08632177821875833</v>
+        <v>0.08683471212026161</v>
       </c>
       <c r="T22">
-        <v>0.8122047442896205</v>
+        <v>0.8224858170021475</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.04942169060698909</v>
+        <v>0.04706827676856103</v>
       </c>
       <c r="W22">
-        <v>0.224146365354872</v>
+        <v>0.2247013003379733</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.1976867624279564</v>
+        <v>0.1882731070742442</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1157866956459811</v>
+        <v>0.1176866956459811</v>
       </c>
       <c r="C23">
-        <v>95.05813767612911</v>
+        <v>90.67060571995881</v>
       </c>
       <c r="D23">
-        <v>77.9377376761291</v>
+        <v>75.87780571995881</v>
       </c>
       <c r="E23">
-        <v>47.81959999999999</v>
+        <v>50.1472</v>
       </c>
       <c r="F23">
-        <v>48.8796</v>
+        <v>51.2072</v>
       </c>
       <c r="G23">
         <v>66</v>
@@ -3161,37 +3161,37 @@
         <v>2.17</v>
       </c>
       <c r="M23">
-        <v>11.52580968</v>
+        <v>12.07465776</v>
       </c>
       <c r="N23">
-        <v>-9.35580968</v>
+        <v>-9.904657760000001</v>
       </c>
       <c r="O23">
-        <v>-2.33895242</v>
+        <v>-2.47616444</v>
       </c>
       <c r="P23">
-        <v>-7.01685726</v>
+        <v>-7.428493320000001</v>
       </c>
       <c r="Q23">
-        <v>-5.87685726</v>
+        <v>-6.288493320000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08683471212026161</v>
+        <v>0.08736079817308548</v>
       </c>
       <c r="T23">
-        <v>0.8224858170021474</v>
+        <v>0.8330305069637134</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.04706827676856104</v>
+        <v>0.04492880964271736</v>
       </c>
       <c r="W23">
-        <v>0.2247013003379733</v>
+        <v>0.2252057866862472</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.1882731070742442</v>
+        <v>0.1797152385708695</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1176866956459811</v>
+        <v>0.1195866956459811</v>
       </c>
       <c r="C24">
-        <v>90.67060571995881</v>
+        <v>86.38915984563451</v>
       </c>
       <c r="D24">
-        <v>75.87780571995881</v>
+        <v>73.92395984563449</v>
       </c>
       <c r="E24">
-        <v>50.1472</v>
+        <v>52.47479999999999</v>
       </c>
       <c r="F24">
-        <v>51.2072</v>
+        <v>53.5348</v>
       </c>
       <c r="G24">
         <v>66</v>
@@ -3243,37 +3243,37 @@
         <v>2.17</v>
       </c>
       <c r="M24">
-        <v>12.07465776</v>
+        <v>12.62350584</v>
       </c>
       <c r="N24">
-        <v>-9.904657760000001</v>
+        <v>-10.45350584</v>
       </c>
       <c r="O24">
-        <v>-2.47616444</v>
+        <v>-2.61337646</v>
       </c>
       <c r="P24">
-        <v>-7.428493320000001</v>
+        <v>-7.84012938</v>
       </c>
       <c r="Q24">
-        <v>-6.288493320000001</v>
+        <v>-6.70012938</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08736079817308548</v>
+        <v>0.08790054879870998</v>
       </c>
       <c r="T24">
-        <v>0.8330305069637134</v>
+        <v>0.8438490849762292</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.04492880964271736</v>
+        <v>0.04297538313651226</v>
       </c>
       <c r="W24">
-        <v>0.2252057866862472</v>
+        <v>0.2256664046564104</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.1797152385708695</v>
+        <v>0.171901532546049</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1195866956459811</v>
+        <v>0.1214866956459811</v>
       </c>
       <c r="C25">
-        <v>86.38915984563451</v>
+        <v>82.20581066134358</v>
       </c>
       <c r="D25">
-        <v>73.92395984563449</v>
+        <v>72.06821066134357</v>
       </c>
       <c r="E25">
-        <v>52.47479999999999</v>
+        <v>54.8024</v>
       </c>
       <c r="F25">
-        <v>53.5348</v>
+        <v>55.8624</v>
       </c>
       <c r="G25">
         <v>66</v>
@@ -3325,37 +3325,37 @@
         <v>2.17</v>
       </c>
       <c r="M25">
-        <v>12.62350584</v>
+        <v>13.17235392</v>
       </c>
       <c r="N25">
-        <v>-10.45350584</v>
+        <v>-11.00235392</v>
       </c>
       <c r="O25">
-        <v>-2.61337646</v>
+        <v>-2.75058848</v>
       </c>
       <c r="P25">
-        <v>-7.84012938</v>
+        <v>-8.25176544</v>
       </c>
       <c r="Q25">
-        <v>-6.70012938</v>
+        <v>-7.111765439999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08790054879870998</v>
+        <v>0.08845450338816668</v>
       </c>
       <c r="T25">
-        <v>0.8438490849762292</v>
+        <v>0.854952362410127</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.04297538313651226</v>
+        <v>0.04118474217249091</v>
       </c>
       <c r="W25">
-        <v>0.2256664046564104</v>
+        <v>0.2260886377957267</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.171901532546049</v>
+        <v>0.1647389686899636</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1214866956459811</v>
+        <v>0.1233866956459811</v>
       </c>
       <c r="C26">
-        <v>82.20581066134359</v>
+        <v>78.11335137565695</v>
       </c>
       <c r="D26">
-        <v>72.06821066134357</v>
+        <v>70.30335137565694</v>
       </c>
       <c r="E26">
-        <v>54.80239999999999</v>
+        <v>57.13</v>
       </c>
       <c r="F26">
-        <v>55.86239999999999</v>
+        <v>58.19</v>
       </c>
       <c r="G26">
         <v>66</v>
@@ -3407,37 +3407,37 @@
         <v>2.17</v>
       </c>
       <c r="M26">
-        <v>13.17235392</v>
+        <v>13.721202</v>
       </c>
       <c r="N26">
-        <v>-11.00235392</v>
+        <v>-11.551202</v>
       </c>
       <c r="O26">
-        <v>-2.75058848</v>
+        <v>-2.8878005</v>
       </c>
       <c r="P26">
-        <v>-8.25176544</v>
+        <v>-8.663401499999999</v>
       </c>
       <c r="Q26">
-        <v>-7.111765439999999</v>
+        <v>-7.523401499999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08845450338816668</v>
+        <v>0.0890232301000089</v>
       </c>
       <c r="T26">
-        <v>0.8549523624101268</v>
+        <v>0.8663517272422619</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.04118474217249091</v>
+        <v>0.03953735248559127</v>
       </c>
       <c r="W26">
-        <v>0.2260886377957267</v>
+        <v>0.2264770922838976</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.1647389686899636</v>
+        <v>0.1581494099423651</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1233866956459811</v>
+        <v>0.1252866956459811</v>
       </c>
       <c r="C27">
-        <v>78.11335137565695</v>
+        <v>74.10526426359139</v>
       </c>
       <c r="D27">
-        <v>70.30335137565694</v>
+        <v>68.62286426359138</v>
       </c>
       <c r="E27">
-        <v>57.13</v>
+        <v>59.4576</v>
       </c>
       <c r="F27">
-        <v>58.19</v>
+        <v>60.5176</v>
       </c>
       <c r="G27">
         <v>66</v>
@@ -3489,37 +3489,37 @@
         <v>2.17</v>
       </c>
       <c r="M27">
-        <v>13.721202</v>
+        <v>14.27005008</v>
       </c>
       <c r="N27">
-        <v>-11.551202</v>
+        <v>-12.10005008</v>
       </c>
       <c r="O27">
-        <v>-2.8878005</v>
+        <v>-3.02501252</v>
       </c>
       <c r="P27">
-        <v>-8.663401499999999</v>
+        <v>-9.07503756</v>
       </c>
       <c r="Q27">
-        <v>-7.523401499999999</v>
+        <v>-7.93503756</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0890232301000089</v>
+        <v>0.08960732780406308</v>
       </c>
       <c r="T27">
-        <v>0.8663517272422619</v>
+        <v>0.878059183015806</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.03953735248559127</v>
+        <v>0.0380166850822993</v>
       </c>
       <c r="W27">
-        <v>0.2264770922838976</v>
+        <v>0.2268356656575938</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.1581494099423651</v>
+        <v>0.1520667403291972</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1252866956459811</v>
+        <v>0.1271866956459811</v>
       </c>
       <c r="C28">
-        <v>74.10526426359139</v>
+        <v>70.17564023416068</v>
       </c>
       <c r="D28">
-        <v>68.62286426359138</v>
+        <v>67.0208402341607</v>
       </c>
       <c r="E28">
-        <v>59.4576</v>
+        <v>61.7852</v>
       </c>
       <c r="F28">
-        <v>60.5176</v>
+        <v>62.8452</v>
       </c>
       <c r="G28">
         <v>66</v>
@@ -3571,37 +3571,37 @@
         <v>2.17</v>
       </c>
       <c r="M28">
-        <v>14.27005008</v>
+        <v>14.81889816</v>
       </c>
       <c r="N28">
-        <v>-12.10005008</v>
+        <v>-12.64889816</v>
       </c>
       <c r="O28">
-        <v>-3.02501252</v>
+        <v>-3.16222454</v>
       </c>
       <c r="P28">
-        <v>-9.07503756</v>
+        <v>-9.486673619999999</v>
       </c>
       <c r="Q28">
-        <v>-7.93503756</v>
+        <v>-8.346673619999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08960732780406308</v>
+        <v>0.09020742818494065</v>
       </c>
       <c r="T28">
-        <v>0.878059183015806</v>
+        <v>0.8900873910023238</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.0380166850822993</v>
+        <v>0.03660865970888081</v>
       </c>
       <c r="W28">
-        <v>0.2268356656575938</v>
+        <v>0.2271676780406459</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.1520667403291972</v>
+        <v>0.1464346388355232</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1271866956459811</v>
+        <v>0.1290866956459811</v>
       </c>
       <c r="C29">
-        <v>70.17564023416068</v>
+        <v>66.31910940724715</v>
       </c>
       <c r="D29">
-        <v>67.0208402341607</v>
+        <v>65.49190940724716</v>
       </c>
       <c r="E29">
-        <v>61.7852</v>
+        <v>64.11280000000001</v>
       </c>
       <c r="F29">
-        <v>62.8452</v>
+        <v>65.17280000000001</v>
       </c>
       <c r="G29">
         <v>66</v>
@@ -3653,37 +3653,37 @@
         <v>2.17</v>
       </c>
       <c r="M29">
-        <v>14.81889816</v>
+        <v>15.36774624</v>
       </c>
       <c r="N29">
-        <v>-12.64889816</v>
+        <v>-13.19774624</v>
       </c>
       <c r="O29">
-        <v>-3.16222454</v>
+        <v>-3.299436560000001</v>
       </c>
       <c r="P29">
-        <v>-9.486673619999999</v>
+        <v>-9.898309680000002</v>
       </c>
       <c r="Q29">
-        <v>-8.346673619999999</v>
+        <v>-8.758309680000002</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09020742818494065</v>
+        <v>0.0908241980208426</v>
       </c>
       <c r="T29">
-        <v>0.8900873910023238</v>
+        <v>0.9024497158773562</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.03660865970888081</v>
+        <v>0.03530120757642077</v>
       </c>
       <c r="W29">
-        <v>0.2271676780406459</v>
+        <v>0.22747597525348</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.1464346388355232</v>
+        <v>0.1412048303056831</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1290866956459811</v>
+        <v>0.1309866956459811</v>
       </c>
       <c r="C30">
-        <v>66.31910940724715</v>
+        <v>62.53078098093404</v>
       </c>
       <c r="D30">
-        <v>65.49190940724716</v>
+        <v>64.03118098093402</v>
       </c>
       <c r="E30">
-        <v>64.11280000000001</v>
+        <v>66.4404</v>
       </c>
       <c r="F30">
-        <v>65.17280000000001</v>
+        <v>67.5004</v>
       </c>
       <c r="G30">
         <v>66</v>
@@ -3735,37 +3735,37 @@
         <v>2.17</v>
       </c>
       <c r="M30">
-        <v>15.36774624</v>
+        <v>15.91659432</v>
       </c>
       <c r="N30">
-        <v>-13.19774624</v>
+        <v>-13.74659432</v>
       </c>
       <c r="O30">
-        <v>-3.299436560000001</v>
+        <v>-3.43664858</v>
       </c>
       <c r="P30">
-        <v>-9.898309680000002</v>
+        <v>-10.30994574</v>
       </c>
       <c r="Q30">
-        <v>-8.758309680000002</v>
+        <v>-9.169945739999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0908241980208426</v>
+        <v>0.09145834165493898</v>
       </c>
       <c r="T30">
-        <v>0.9024497158773562</v>
+        <v>0.9151602752559105</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.03530120757642077</v>
+        <v>0.0340839245565442</v>
       </c>
       <c r="W30">
-        <v>0.22747597525348</v>
+        <v>0.2277630105895669</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1412048303056831</v>
+        <v>0.1363356982261769</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1309866956459811</v>
+        <v>0.132886695645981</v>
       </c>
       <c r="C31">
-        <v>62.53078098093404</v>
+        <v>58.80619097044688</v>
       </c>
       <c r="D31">
-        <v>64.03118098093404</v>
+        <v>62.63419097044687</v>
       </c>
       <c r="E31">
-        <v>66.4404</v>
+        <v>68.76799999999999</v>
       </c>
       <c r="F31">
-        <v>67.5004</v>
+        <v>69.82799999999999</v>
       </c>
       <c r="G31">
         <v>66</v>
@@ -3817,37 +3817,37 @@
         <v>2.17</v>
       </c>
       <c r="M31">
-        <v>15.91659432</v>
+        <v>16.4654424</v>
       </c>
       <c r="N31">
-        <v>-13.74659432</v>
+        <v>-14.2954424</v>
       </c>
       <c r="O31">
-        <v>-3.43664858</v>
+        <v>-3.573860599999999</v>
       </c>
       <c r="P31">
-        <v>-10.30994574</v>
+        <v>-10.7215818</v>
       </c>
       <c r="Q31">
-        <v>-9.169945739999999</v>
+        <v>-9.581581799999997</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09145834165493898</v>
+        <v>0.09211060367858095</v>
       </c>
       <c r="T31">
-        <v>0.9151602752559105</v>
+        <v>0.928233993473852</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.0340839245565442</v>
+        <v>0.03294779373799273</v>
       </c>
       <c r="W31">
-        <v>0.2277630105895669</v>
+        <v>0.2280309102365813</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1363356982261769</v>
+        <v>0.1317911749519709</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.132886695645981</v>
+        <v>0.1347866956459811</v>
       </c>
       <c r="C32">
-        <v>58.80619097044688</v>
+        <v>55.14125664220873</v>
       </c>
       <c r="D32">
-        <v>62.63419097044687</v>
+        <v>61.29685664220872</v>
       </c>
       <c r="E32">
-        <v>68.76799999999999</v>
+        <v>71.09559999999999</v>
       </c>
       <c r="F32">
-        <v>69.82799999999999</v>
+        <v>72.15559999999999</v>
       </c>
       <c r="G32">
         <v>66</v>
@@ -3899,37 +3899,37 @@
         <v>2.17</v>
       </c>
       <c r="M32">
-        <v>16.4654424</v>
+        <v>17.01429048</v>
       </c>
       <c r="N32">
-        <v>-14.2954424</v>
+        <v>-14.84429048</v>
       </c>
       <c r="O32">
-        <v>-3.573860599999999</v>
+        <v>-3.71107262</v>
       </c>
       <c r="P32">
-        <v>-10.7215818</v>
+        <v>-11.13321786</v>
       </c>
       <c r="Q32">
-        <v>-9.581581799999997</v>
+        <v>-9.99321786</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09211060367858095</v>
+        <v>0.09278177184783576</v>
       </c>
       <c r="T32">
-        <v>0.928233993473852</v>
+        <v>0.9416866600459369</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.03294779373799273</v>
+        <v>0.03188496168192845</v>
       </c>
       <c r="W32">
-        <v>0.2280309102365813</v>
+        <v>0.2282815260354013</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1317911749519709</v>
+        <v>0.1275398467277138</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1347866956459811</v>
+        <v>0.1366866956459811</v>
       </c>
       <c r="C33">
-        <v>55.14125664220873</v>
+        <v>51.53223666327314</v>
       </c>
       <c r="D33">
-        <v>61.29685664220872</v>
+        <v>60.01543666327314</v>
       </c>
       <c r="E33">
-        <v>71.09559999999999</v>
+        <v>73.42319999999999</v>
       </c>
       <c r="F33">
-        <v>72.15559999999999</v>
+        <v>74.4832</v>
       </c>
       <c r="G33">
         <v>66</v>
@@ -3981,37 +3981,37 @@
         <v>2.17</v>
       </c>
       <c r="M33">
-        <v>17.01429048</v>
+        <v>17.56313856</v>
       </c>
       <c r="N33">
-        <v>-14.84429048</v>
+        <v>-15.39313856</v>
       </c>
       <c r="O33">
-        <v>-3.71107262</v>
+        <v>-3.84828464</v>
       </c>
       <c r="P33">
-        <v>-11.13321786</v>
+        <v>-11.54485392</v>
       </c>
       <c r="Q33">
-        <v>-9.99321786</v>
+        <v>-10.40485392</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09278177184783576</v>
+        <v>0.09347268025736276</v>
       </c>
       <c r="T33">
-        <v>0.9416866600459369</v>
+        <v>0.9555349932819066</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.03188496168192845</v>
+        <v>0.03088855662936819</v>
       </c>
       <c r="W33">
-        <v>0.2282815260354013</v>
+        <v>0.228516478346795</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1275398467277138</v>
+        <v>0.1235542265174727</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1366866956459811</v>
+        <v>0.1385866956459811</v>
       </c>
       <c r="C34">
-        <v>51.53223666327314</v>
+        <v>47.97569614689471</v>
       </c>
       <c r="D34">
-        <v>60.01543666327314</v>
+        <v>58.78649614689471</v>
       </c>
       <c r="E34">
-        <v>73.42319999999999</v>
+        <v>75.7508</v>
       </c>
       <c r="F34">
-        <v>74.4832</v>
+        <v>76.8108</v>
       </c>
       <c r="G34">
         <v>66</v>
@@ -4063,37 +4063,37 @@
         <v>2.17</v>
       </c>
       <c r="M34">
-        <v>17.56313856</v>
+        <v>18.11198664</v>
       </c>
       <c r="N34">
-        <v>-15.39313856</v>
+        <v>-15.94198664</v>
       </c>
       <c r="O34">
-        <v>-3.84828464</v>
+        <v>-3.98549666</v>
       </c>
       <c r="P34">
-        <v>-11.54485392</v>
+        <v>-11.95648998</v>
       </c>
       <c r="Q34">
-        <v>-10.40485392</v>
+        <v>-10.81648998</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09347268025736276</v>
+        <v>0.09418421279851744</v>
       </c>
       <c r="T34">
-        <v>0.9555349932819066</v>
+        <v>0.9697967095995471</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.03088855662936819</v>
+        <v>0.02995253976181157</v>
       </c>
       <c r="W34">
-        <v>0.228516478346795</v>
+        <v>0.2287371911241649</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1235542265174727</v>
+        <v>0.1198101590472462</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1385866956459811</v>
+        <v>0.1404866956459811</v>
       </c>
       <c r="C35">
-        <v>47.97569614689471</v>
+        <v>44.46847590651048</v>
       </c>
       <c r="D35">
-        <v>58.78649614689471</v>
+        <v>57.60687590651049</v>
       </c>
       <c r="E35">
-        <v>75.7508</v>
+        <v>78.0784</v>
       </c>
       <c r="F35">
-        <v>76.8108</v>
+        <v>79.1384</v>
       </c>
       <c r="G35">
         <v>66</v>
@@ -4145,37 +4145,37 @@
         <v>2.17</v>
       </c>
       <c r="M35">
-        <v>18.11198664</v>
+        <v>18.66083472</v>
       </c>
       <c r="N35">
-        <v>-15.94198664</v>
+        <v>-16.49083472</v>
       </c>
       <c r="O35">
-        <v>-3.98549666</v>
+        <v>-4.122708680000001</v>
       </c>
       <c r="P35">
-        <v>-11.95648998</v>
+        <v>-12.36812604</v>
       </c>
       <c r="Q35">
-        <v>-10.81648998</v>
+        <v>-11.22812604</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09418421279851744</v>
+        <v>0.09491730693182832</v>
       </c>
       <c r="T35">
-        <v>0.9697967095995471</v>
+        <v>0.9844905991389342</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.02995253976181157</v>
+        <v>0.02907158270999358</v>
       </c>
       <c r="W35">
-        <v>0.2287371911241649</v>
+        <v>0.2289449207969835</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1198101590472462</v>
+        <v>0.1162863308399742</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1404866956459811</v>
+        <v>0.1423866956459811</v>
       </c>
       <c r="C36">
-        <v>44.46847590651048</v>
+        <v>41.00766533863322</v>
       </c>
       <c r="D36">
-        <v>57.60687590651049</v>
+        <v>56.47366533863323</v>
       </c>
       <c r="E36">
-        <v>78.0784</v>
+        <v>80.40600000000001</v>
       </c>
       <c r="F36">
-        <v>79.1384</v>
+        <v>81.46600000000001</v>
       </c>
       <c r="G36">
         <v>66</v>
@@ -4227,37 +4227,37 @@
         <v>2.17</v>
       </c>
       <c r="M36">
-        <v>18.66083472</v>
+        <v>19.2096828</v>
       </c>
       <c r="N36">
-        <v>-16.49083472</v>
+        <v>-17.0396828</v>
       </c>
       <c r="O36">
-        <v>-4.122708680000001</v>
+        <v>-4.2599207</v>
       </c>
       <c r="P36">
-        <v>-12.36812604</v>
+        <v>-12.7797621</v>
       </c>
       <c r="Q36">
-        <v>-11.22812604</v>
+        <v>-11.6397621</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09491730693182832</v>
+        <v>0.09567295780770259</v>
       </c>
       <c r="T36">
-        <v>0.9844905991389342</v>
+        <v>0.9996366083564563</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.02907158270999358</v>
+        <v>0.02824096606113662</v>
       </c>
       <c r="W36">
-        <v>0.2289449207969835</v>
+        <v>0.229140780202784</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1162863308399742</v>
+        <v>0.1129638642445466</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1423866956459811</v>
+        <v>0.1442866956459811</v>
       </c>
       <c r="C37">
-        <v>41.00766533863322</v>
+        <v>37.59057844459524</v>
       </c>
       <c r="D37">
-        <v>56.47366533863323</v>
+        <v>55.38417844459526</v>
       </c>
       <c r="E37">
-        <v>80.40600000000001</v>
+        <v>82.73360000000001</v>
       </c>
       <c r="F37">
-        <v>81.46600000000001</v>
+        <v>83.79360000000001</v>
       </c>
       <c r="G37">
         <v>66</v>
@@ -4309,37 +4309,37 @@
         <v>2.17</v>
       </c>
       <c r="M37">
-        <v>19.2096828</v>
+        <v>19.75853088</v>
       </c>
       <c r="N37">
-        <v>-17.0396828</v>
+        <v>-17.58853088</v>
       </c>
       <c r="O37">
-        <v>-4.2599207</v>
+        <v>-4.39713272</v>
       </c>
       <c r="P37">
-        <v>-12.7797621</v>
+        <v>-13.19139816</v>
       </c>
       <c r="Q37">
-        <v>-11.6397621</v>
+        <v>-12.05139816</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09567295780770259</v>
+        <v>0.09645222277344795</v>
       </c>
       <c r="T37">
-        <v>0.9996366083564563</v>
+        <v>1.015255930362026</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.02824096606113662</v>
+        <v>0.02745649478166061</v>
       </c>
       <c r="W37">
-        <v>0.229140780202784</v>
+        <v>0.2293257585304845</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1129638642445466</v>
+        <v>0.1098259791266425</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1442866956459811</v>
+        <v>0.1461866956459811</v>
       </c>
       <c r="C38">
-        <v>37.59057844459528</v>
+        <v>34.21473257528376</v>
       </c>
       <c r="D38">
-        <v>55.38417844459528</v>
+        <v>54.33593257528376</v>
       </c>
       <c r="E38">
-        <v>82.7336</v>
+        <v>85.0612</v>
       </c>
       <c r="F38">
-        <v>83.7936</v>
+        <v>86.1212</v>
       </c>
       <c r="G38">
         <v>66</v>
@@ -4391,37 +4391,37 @@
         <v>2.17</v>
       </c>
       <c r="M38">
-        <v>19.75853088</v>
+        <v>20.30737896</v>
       </c>
       <c r="N38">
-        <v>-17.58853088</v>
+        <v>-18.13737896</v>
       </c>
       <c r="O38">
-        <v>-4.39713272</v>
+        <v>-4.53434474</v>
       </c>
       <c r="P38">
-        <v>-13.19139816</v>
+        <v>-13.60303422</v>
       </c>
       <c r="Q38">
-        <v>-12.05139816</v>
+        <v>-12.46303422</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09645222277344792</v>
+        <v>0.0972562263095344</v>
       </c>
       <c r="T38">
-        <v>1.015255930362026</v>
+        <v>1.031371103859836</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.02745649478166061</v>
+        <v>0.02671442735512924</v>
       </c>
       <c r="W38">
-        <v>0.2293257585304845</v>
+        <v>0.2295007380296605</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1098259791266424</v>
+        <v>0.1068577094205171</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1461866956459811</v>
+        <v>0.1480866956459811</v>
       </c>
       <c r="C39">
-        <v>34.21473257528376</v>
+        <v>30.87782954480606</v>
       </c>
       <c r="D39">
-        <v>54.33593257528376</v>
+        <v>53.32662954480606</v>
       </c>
       <c r="E39">
-        <v>85.0612</v>
+        <v>87.38879999999999</v>
       </c>
       <c r="F39">
-        <v>86.1212</v>
+        <v>88.44879999999999</v>
       </c>
       <c r="G39">
         <v>66</v>
@@ -4473,37 +4473,37 @@
         <v>2.17</v>
       </c>
       <c r="M39">
-        <v>20.30737896</v>
+        <v>20.85622704</v>
       </c>
       <c r="N39">
-        <v>-18.13737896</v>
+        <v>-18.68622704</v>
       </c>
       <c r="O39">
-        <v>-4.53434474</v>
+        <v>-4.67155676</v>
       </c>
       <c r="P39">
-        <v>-13.60303422</v>
+        <v>-14.01467028</v>
       </c>
       <c r="Q39">
-        <v>-12.46303422</v>
+        <v>-12.87467028</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0972562263095344</v>
+        <v>0.09808616544355915</v>
       </c>
       <c r="T39">
-        <v>1.031371103859836</v>
+        <v>1.048006121664026</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.02671442735512924</v>
+        <v>0.02601141610894163</v>
       </c>
       <c r="W39">
-        <v>0.2295007380296605</v>
+        <v>0.2296665080815116</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1068577094205171</v>
+        <v>0.1040456644357666</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1480866956459811</v>
+        <v>0.1499866956459811</v>
       </c>
       <c r="C40">
-        <v>30.87782954480606</v>
+        <v>27.57773881067806</v>
       </c>
       <c r="D40">
-        <v>53.32662954480606</v>
+        <v>52.35413881067806</v>
       </c>
       <c r="E40">
-        <v>87.38879999999999</v>
+        <v>89.71639999999999</v>
       </c>
       <c r="F40">
-        <v>88.44879999999999</v>
+        <v>90.7764</v>
       </c>
       <c r="G40">
         <v>66</v>
@@ -4555,37 +4555,37 @@
         <v>2.17</v>
       </c>
       <c r="M40">
-        <v>20.85622704</v>
+        <v>21.40507512</v>
       </c>
       <c r="N40">
-        <v>-18.68622704</v>
+        <v>-19.23507512</v>
       </c>
       <c r="O40">
-        <v>-4.67155676</v>
+        <v>-4.808768779999999</v>
       </c>
       <c r="P40">
-        <v>-14.01467028</v>
+        <v>-14.42630634</v>
       </c>
       <c r="Q40">
-        <v>-12.87467028</v>
+        <v>-13.28630634</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09808616544355915</v>
+        <v>0.09894331569673226</v>
       </c>
       <c r="T40">
-        <v>1.048006121664026</v>
+        <v>1.065186549888027</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.02601141610894163</v>
+        <v>0.02534445672153287</v>
       </c>
       <c r="W40">
-        <v>0.2296665080815116</v>
+        <v>0.2298237771050626</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1040456644357666</v>
+        <v>0.1013778268861316</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1499866956459811</v>
+        <v>0.1518866956459811</v>
       </c>
       <c r="C41">
-        <v>27.57773881067806</v>
+        <v>24.31248246145744</v>
       </c>
       <c r="D41">
-        <v>52.35413881067806</v>
+        <v>51.41648246145743</v>
       </c>
       <c r="E41">
-        <v>89.71639999999999</v>
+        <v>92.044</v>
       </c>
       <c r="F41">
-        <v>90.7764</v>
+        <v>93.104</v>
       </c>
       <c r="G41">
         <v>66</v>
@@ -4637,37 +4637,37 @@
         <v>2.17</v>
       </c>
       <c r="M41">
-        <v>21.40507512</v>
+        <v>21.9539232</v>
       </c>
       <c r="N41">
-        <v>-19.23507512</v>
+        <v>-19.7839232</v>
       </c>
       <c r="O41">
-        <v>-4.808768779999999</v>
+        <v>-4.945980800000001</v>
       </c>
       <c r="P41">
-        <v>-14.42630634</v>
+        <v>-14.8379424</v>
       </c>
       <c r="Q41">
-        <v>-13.28630634</v>
+        <v>-13.6979424</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09894331569673226</v>
+        <v>0.09982903762501114</v>
       </c>
       <c r="T41">
-        <v>1.065186549888027</v>
+        <v>1.082939659052828</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.02534445672153287</v>
+        <v>0.02471084530349454</v>
       </c>
       <c r="W41">
-        <v>0.2298237771050626</v>
+        <v>0.229973182677436</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1013778268861316</v>
+        <v>0.09884338121397807</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1518866956459811</v>
+        <v>0.1537866956459811</v>
       </c>
       <c r="C42">
-        <v>24.31248246145744</v>
+        <v>21.08022178921097</v>
       </c>
       <c r="D42">
-        <v>51.41648246145743</v>
+        <v>50.51182178921097</v>
       </c>
       <c r="E42">
-        <v>92.044</v>
+        <v>94.3716</v>
       </c>
       <c r="F42">
-        <v>93.104</v>
+        <v>95.4316</v>
       </c>
       <c r="G42">
         <v>66</v>
@@ -4719,37 +4719,37 @@
         <v>2.17</v>
       </c>
       <c r="M42">
-        <v>21.9539232</v>
+        <v>22.50277128</v>
       </c>
       <c r="N42">
-        <v>-19.7839232</v>
+        <v>-20.33277128</v>
       </c>
       <c r="O42">
-        <v>-4.945980800000001</v>
+        <v>-5.083192820000001</v>
       </c>
       <c r="P42">
-        <v>-14.8379424</v>
+        <v>-15.24957846</v>
       </c>
       <c r="Q42">
-        <v>-13.6979424</v>
+        <v>-14.10957846</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09982903762501114</v>
+        <v>0.100744784025435</v>
       </c>
       <c r="T42">
-        <v>1.082939659052828</v>
+        <v>1.101294568528299</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.02471084530349454</v>
+        <v>0.02410814175950687</v>
       </c>
       <c r="W42">
-        <v>0.229973182677436</v>
+        <v>0.2301153001731083</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.09884338121397807</v>
+        <v>0.09643256703802738</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1537866956459811</v>
+        <v>0.1556866956459811</v>
       </c>
       <c r="C43">
-        <v>21.08022178921097</v>
+        <v>17.87924525499709</v>
       </c>
       <c r="D43">
-        <v>50.51182178921097</v>
+        <v>49.63844525499709</v>
       </c>
       <c r="E43">
-        <v>94.3716</v>
+        <v>96.6992</v>
       </c>
       <c r="F43">
-        <v>95.4316</v>
+        <v>97.75920000000001</v>
       </c>
       <c r="G43">
         <v>66</v>
@@ -4801,37 +4801,37 @@
         <v>2.17</v>
       </c>
       <c r="M43">
-        <v>22.50277128</v>
+        <v>23.05161936</v>
       </c>
       <c r="N43">
-        <v>-20.33277128</v>
+        <v>-20.88161936</v>
       </c>
       <c r="O43">
-        <v>-5.083192820000001</v>
+        <v>-5.22040484</v>
       </c>
       <c r="P43">
-        <v>-15.24957846</v>
+        <v>-15.66121452</v>
       </c>
       <c r="Q43">
-        <v>-14.10957846</v>
+        <v>-14.52121452</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.100744784025435</v>
+        <v>0.1016921078879425</v>
       </c>
       <c r="T43">
-        <v>1.101294568528299</v>
+        <v>1.120282405916718</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.02410814175950687</v>
+        <v>0.02353413838428052</v>
       </c>
       <c r="W43">
-        <v>0.2301153001731083</v>
+        <v>0.2302506501689867</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.09643256703802738</v>
+        <v>0.09413655353712214</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1556866956459811</v>
+        <v>0.1575866956459811</v>
       </c>
       <c r="C44">
-        <v>17.87924525499713</v>
+        <v>14.70795768162812</v>
       </c>
       <c r="D44">
-        <v>49.63844525499712</v>
+        <v>48.79475768162811</v>
       </c>
       <c r="E44">
-        <v>96.69919999999999</v>
+        <v>99.02679999999999</v>
       </c>
       <c r="F44">
-        <v>97.75919999999999</v>
+        <v>100.0868</v>
       </c>
       <c r="G44">
         <v>66</v>
@@ -4883,37 +4883,37 @@
         <v>2.17</v>
       </c>
       <c r="M44">
-        <v>23.05161936</v>
+        <v>23.60046744</v>
       </c>
       <c r="N44">
-        <v>-20.88161936</v>
+        <v>-21.43046744</v>
       </c>
       <c r="O44">
-        <v>-5.22040484</v>
+        <v>-5.35761686</v>
       </c>
       <c r="P44">
-        <v>-15.66121452</v>
+        <v>-16.07285058</v>
       </c>
       <c r="Q44">
-        <v>-14.52121452</v>
+        <v>-14.93285058</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1016921078879425</v>
+        <v>0.1026726711842222</v>
       </c>
       <c r="T44">
-        <v>1.120282405916718</v>
+        <v>1.139936483213502</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.02353413838428052</v>
+        <v>0.02298683284046004</v>
       </c>
       <c r="W44">
-        <v>0.2302506501689867</v>
+        <v>0.2303797048162196</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.09413655353712203</v>
+        <v>0.09194733136184008</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1575866956459811</v>
+        <v>0.1594866956459811</v>
       </c>
       <c r="C45">
-        <v>14.70795768162812</v>
+        <v>11.56487053013423</v>
       </c>
       <c r="D45">
-        <v>48.79475768162811</v>
+        <v>47.97927053013423</v>
       </c>
       <c r="E45">
-        <v>99.02679999999999</v>
+        <v>101.3544</v>
       </c>
       <c r="F45">
-        <v>100.0868</v>
+        <v>102.4144</v>
       </c>
       <c r="G45">
         <v>66</v>
@@ -4965,37 +4965,37 @@
         <v>2.17</v>
       </c>
       <c r="M45">
-        <v>23.60046744</v>
+        <v>24.14931552</v>
       </c>
       <c r="N45">
-        <v>-21.43046744</v>
+        <v>-21.97931552</v>
       </c>
       <c r="O45">
-        <v>-5.35761686</v>
+        <v>-5.49482888</v>
       </c>
       <c r="P45">
-        <v>-16.07285058</v>
+        <v>-16.48448664</v>
       </c>
       <c r="Q45">
-        <v>-14.93285058</v>
+        <v>-15.34448664</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1026726711842222</v>
+        <v>0.1036882545982262</v>
       </c>
       <c r="T45">
-        <v>1.139936483213502</v>
+        <v>1.160292491842315</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.02298683284046004</v>
+        <v>0.02246440482135868</v>
       </c>
       <c r="W45">
-        <v>0.2303797048162196</v>
+        <v>0.2305028933431236</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.09194733136184008</v>
+        <v>0.08985761928543479</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1594866956459811</v>
+        <v>0.1613866956459811</v>
       </c>
       <c r="C46">
-        <v>11.56487053013423</v>
+        <v>8.448593135233509</v>
       </c>
       <c r="D46">
-        <v>47.97927053013423</v>
+        <v>47.19059313523352</v>
       </c>
       <c r="E46">
-        <v>101.3544</v>
+        <v>103.682</v>
       </c>
       <c r="F46">
-        <v>102.4144</v>
+        <v>104.742</v>
       </c>
       <c r="G46">
         <v>66</v>
@@ -5047,37 +5047,37 @@
         <v>2.17</v>
       </c>
       <c r="M46">
-        <v>24.14931552</v>
+        <v>24.6981636</v>
       </c>
       <c r="N46">
-        <v>-21.97931552</v>
+        <v>-22.5281636</v>
       </c>
       <c r="O46">
-        <v>-5.49482888</v>
+        <v>-5.6320409</v>
       </c>
       <c r="P46">
-        <v>-16.48448664</v>
+        <v>-16.8961227</v>
       </c>
       <c r="Q46">
-        <v>-15.34448664</v>
+        <v>-15.7561227</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1036882545982262</v>
+        <v>0.104740768318194</v>
       </c>
       <c r="T46">
-        <v>1.160292491842315</v>
+        <v>1.181388718966721</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02246440482135868</v>
+        <v>0.02196519582532849</v>
       </c>
       <c r="W46">
-        <v>0.2305028933431236</v>
+        <v>0.2306206068243875</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.08985761928543479</v>
+        <v>0.08786078330131397</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1613866956459811</v>
+        <v>0.1632866956459811</v>
       </c>
       <c r="C47">
-        <v>8.448593135233509</v>
+        <v>5.357824791243999</v>
       </c>
       <c r="D47">
-        <v>47.19059313523352</v>
+        <v>46.427424791244</v>
       </c>
       <c r="E47">
-        <v>103.682</v>
+        <v>106.0096</v>
       </c>
       <c r="F47">
-        <v>104.742</v>
+        <v>107.0696</v>
       </c>
       <c r="G47">
         <v>66</v>
@@ -5129,37 +5129,37 @@
         <v>2.17</v>
       </c>
       <c r="M47">
-        <v>24.6981636</v>
+        <v>25.24701168</v>
       </c>
       <c r="N47">
-        <v>-22.5281636</v>
+        <v>-23.07701168</v>
       </c>
       <c r="O47">
-        <v>-5.6320409</v>
+        <v>-5.76925292</v>
       </c>
       <c r="P47">
-        <v>-16.8961227</v>
+        <v>-17.30775876</v>
       </c>
       <c r="Q47">
-        <v>-15.7561227</v>
+        <v>-16.16775876</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.104740768318194</v>
+        <v>0.1058322640277901</v>
       </c>
       <c r="T47">
-        <v>1.181388718966721</v>
+        <v>1.203266287836475</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.02196519582532849</v>
+        <v>0.02148769156825613</v>
       </c>
       <c r="W47">
-        <v>0.2306206068243875</v>
+        <v>0.2307332023282052</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.08786078330131397</v>
+        <v>0.08595076627302456</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1632866956459811</v>
+        <v>0.1651866956459811</v>
       </c>
       <c r="C48">
-        <v>5.357824791243999</v>
+        <v>2.291347593696457</v>
       </c>
       <c r="D48">
-        <v>46.427424791244</v>
+        <v>45.68854759369645</v>
       </c>
       <c r="E48">
-        <v>106.0096</v>
+        <v>108.3372</v>
       </c>
       <c r="F48">
-        <v>107.0696</v>
+        <v>109.3972</v>
       </c>
       <c r="G48">
         <v>66</v>
@@ -5211,37 +5211,37 @@
         <v>2.17</v>
       </c>
       <c r="M48">
-        <v>25.24701168</v>
+        <v>25.79585976</v>
       </c>
       <c r="N48">
-        <v>-23.07701168</v>
+        <v>-23.62585976</v>
       </c>
       <c r="O48">
-        <v>-5.76925292</v>
+        <v>-5.906464939999999</v>
       </c>
       <c r="P48">
-        <v>-17.30775876</v>
+        <v>-17.71939482</v>
       </c>
       <c r="Q48">
-        <v>-16.16775876</v>
+        <v>-16.57939482</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1058322640277901</v>
+        <v>0.1069649482547296</v>
       </c>
       <c r="T48">
-        <v>1.203266287836475</v>
+        <v>1.225969425342823</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02148769156825613</v>
+        <v>0.02103050664127196</v>
       </c>
       <c r="W48">
-        <v>0.2307332023282052</v>
+        <v>0.2308410065339881</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.08595076627302456</v>
+        <v>0.08412202656508794</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1651866956459811</v>
+        <v>0.1670866956459811</v>
       </c>
       <c r="C49">
-        <v>2.291347593696457</v>
+        <v>-0.7519800462204955</v>
       </c>
       <c r="D49">
-        <v>45.68854759369645</v>
+        <v>44.97281995377951</v>
       </c>
       <c r="E49">
-        <v>108.3372</v>
+        <v>110.6648</v>
       </c>
       <c r="F49">
-        <v>109.3972</v>
+        <v>111.7248</v>
       </c>
       <c r="G49">
         <v>66</v>
@@ -5293,37 +5293,37 @@
         <v>2.17</v>
       </c>
       <c r="M49">
-        <v>25.79585976</v>
+        <v>26.34470784</v>
       </c>
       <c r="N49">
-        <v>-23.62585976</v>
+        <v>-24.17470784</v>
       </c>
       <c r="O49">
-        <v>-5.906464939999999</v>
+        <v>-6.043676960000001</v>
       </c>
       <c r="P49">
-        <v>-17.71939482</v>
+        <v>-18.13103088</v>
       </c>
       <c r="Q49">
-        <v>-16.57939482</v>
+        <v>-16.99103088</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1069649482547296</v>
+        <v>0.1081411972596282</v>
       </c>
       <c r="T49">
-        <v>1.225969425342823</v>
+        <v>1.24954576044557</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02103050664127196</v>
+        <v>0.02059237108624545</v>
       </c>
       <c r="W49">
-        <v>0.2308410065339881</v>
+        <v>0.2309443188978633</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.08412202656508794</v>
+        <v>0.0823694843449817</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1670866956459811</v>
+        <v>0.1689866956459811</v>
       </c>
       <c r="C50">
-        <v>-0.7519800462204813</v>
+        <v>-3.773229287026041</v>
       </c>
       <c r="D50">
-        <v>44.97281995377951</v>
+        <v>44.27917071297394</v>
       </c>
       <c r="E50">
-        <v>110.6648</v>
+        <v>112.9924</v>
       </c>
       <c r="F50">
-        <v>111.7248</v>
+        <v>114.0524</v>
       </c>
       <c r="G50">
         <v>66</v>
@@ -5375,37 +5375,37 @@
         <v>2.17</v>
       </c>
       <c r="M50">
-        <v>26.34470784</v>
+        <v>26.89355592</v>
       </c>
       <c r="N50">
-        <v>-24.17470784</v>
+        <v>-24.72355592</v>
       </c>
       <c r="O50">
-        <v>-6.043676959999999</v>
+        <v>-6.180888980000001</v>
       </c>
       <c r="P50">
-        <v>-18.13103088</v>
+        <v>-18.54266694</v>
       </c>
       <c r="Q50">
-        <v>-16.99103088</v>
+        <v>-17.40266694</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1081411972596282</v>
+        <v>0.1093635736764837</v>
       </c>
       <c r="T50">
-        <v>1.24954576044557</v>
+        <v>1.274046657709209</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02059237108624546</v>
+        <v>0.02017211861509759</v>
       </c>
       <c r="W50">
-        <v>0.2309443188978633</v>
+        <v>0.23104341443056</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.08236948434498192</v>
+        <v>0.08068847446039029</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1689866956459811</v>
+        <v>0.1708866956459811</v>
       </c>
       <c r="C51">
-        <v>-3.773229287026041</v>
+        <v>-6.773406205939608</v>
       </c>
       <c r="D51">
-        <v>44.27917071297394</v>
+        <v>43.60659379406039</v>
       </c>
       <c r="E51">
-        <v>112.9924</v>
+        <v>115.32</v>
       </c>
       <c r="F51">
-        <v>114.0524</v>
+        <v>116.38</v>
       </c>
       <c r="G51">
         <v>66</v>
@@ -5457,37 +5457,37 @@
         <v>2.17</v>
       </c>
       <c r="M51">
-        <v>26.89355592</v>
+        <v>27.442404</v>
       </c>
       <c r="N51">
-        <v>-24.72355592</v>
+        <v>-25.272404</v>
       </c>
       <c r="O51">
-        <v>-6.180888980000001</v>
+        <v>-6.318101</v>
       </c>
       <c r="P51">
-        <v>-18.54266694</v>
+        <v>-18.954303</v>
       </c>
       <c r="Q51">
-        <v>-17.40266694</v>
+        <v>-17.814303</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1093635736764837</v>
+        <v>0.1106348451500133</v>
       </c>
       <c r="T51">
-        <v>1.274046657709209</v>
+        <v>1.299527590863393</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02017211861509759</v>
+        <v>0.01976867624279564</v>
       </c>
       <c r="W51">
-        <v>0.23104341443056</v>
+        <v>0.2311385461419488</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.08068847446039029</v>
+        <v>0.07907470497118252</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1708866956459811</v>
+        <v>0.1727866956459811</v>
       </c>
       <c r="C52">
-        <v>-6.773406205939608</v>
+        <v>-9.7534566676769</v>
       </c>
       <c r="D52">
-        <v>43.60659379406039</v>
+        <v>42.9541433323231</v>
       </c>
       <c r="E52">
-        <v>115.32</v>
+        <v>117.6476</v>
       </c>
       <c r="F52">
-        <v>116.38</v>
+        <v>118.7076</v>
       </c>
       <c r="G52">
         <v>66</v>
@@ -5539,37 +5539,37 @@
         <v>2.17</v>
       </c>
       <c r="M52">
-        <v>27.442404</v>
+        <v>27.99125208</v>
       </c>
       <c r="N52">
-        <v>-25.272404</v>
+        <v>-25.82125208</v>
       </c>
       <c r="O52">
-        <v>-6.318101</v>
+        <v>-6.45531302</v>
       </c>
       <c r="P52">
-        <v>-18.954303</v>
+        <v>-19.36593906</v>
       </c>
       <c r="Q52">
-        <v>-17.814303</v>
+        <v>-18.22593906</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1106348451500133</v>
+        <v>0.1119580052551157</v>
       </c>
       <c r="T52">
-        <v>1.299527590863393</v>
+        <v>1.326048562105503</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.01976867624279564</v>
+        <v>0.01938105513999572</v>
       </c>
       <c r="W52">
-        <v>0.2311385461419488</v>
+        <v>0.231229947197989</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.07907470497118252</v>
+        <v>0.07752422055998298</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1727866956459811</v>
+        <v>0.1746866956459811</v>
       </c>
       <c r="C53">
-        <v>-9.7534566676769</v>
+        <v>-12.71427076260245</v>
       </c>
       <c r="D53">
-        <v>42.9541433323231</v>
+        <v>42.32092923739755</v>
       </c>
       <c r="E53">
-        <v>117.6476</v>
+        <v>119.9752</v>
       </c>
       <c r="F53">
-        <v>118.7076</v>
+        <v>121.0352</v>
       </c>
       <c r="G53">
         <v>66</v>
@@ -5621,37 +5621,37 @@
         <v>2.17</v>
       </c>
       <c r="M53">
-        <v>27.99125208</v>
+        <v>28.54010016</v>
       </c>
       <c r="N53">
-        <v>-25.82125208</v>
+        <v>-26.37010016</v>
       </c>
       <c r="O53">
-        <v>-6.45531302</v>
+        <v>-6.59252504</v>
       </c>
       <c r="P53">
-        <v>-19.36593906</v>
+        <v>-19.77757512</v>
       </c>
       <c r="Q53">
-        <v>-18.22593906</v>
+        <v>-18.63757512</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1119580052551157</v>
+        <v>0.1133362970312639</v>
       </c>
       <c r="T53">
-        <v>1.326048562105503</v>
+        <v>1.353674573816034</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.01938105513999572</v>
+        <v>0.01900834254114965</v>
       </c>
       <c r="W53">
-        <v>0.231229947197989</v>
+        <v>0.2313178328287969</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.07752422055998298</v>
+        <v>0.07603337016459866</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1746866956459811</v>
+        <v>0.1765866956459811</v>
       </c>
       <c r="C54">
-        <v>-12.71427076260245</v>
+        <v>-15.65668685803094</v>
       </c>
       <c r="D54">
-        <v>42.32092923739755</v>
+        <v>41.70611314196907</v>
       </c>
       <c r="E54">
-        <v>119.9752</v>
+        <v>122.3028</v>
       </c>
       <c r="F54">
-        <v>121.0352</v>
+        <v>123.3628</v>
       </c>
       <c r="G54">
         <v>66</v>
@@ -5703,37 +5703,37 @@
         <v>2.17</v>
       </c>
       <c r="M54">
-        <v>28.54010016</v>
+        <v>29.08894824</v>
       </c>
       <c r="N54">
-        <v>-26.37010016</v>
+        <v>-26.91894824000001</v>
       </c>
       <c r="O54">
-        <v>-6.59252504</v>
+        <v>-6.729737060000001</v>
       </c>
       <c r="P54">
-        <v>-19.77757512</v>
+        <v>-20.18921118</v>
       </c>
       <c r="Q54">
-        <v>-18.63757512</v>
+        <v>-19.04921118</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1133362970312639</v>
+        <v>0.1147732395212908</v>
       </c>
       <c r="T54">
-        <v>1.353674573816034</v>
+        <v>1.382476160492971</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.01900834254114965</v>
+        <v>0.01864969456867513</v>
       </c>
       <c r="W54">
-        <v>0.2313178328287969</v>
+        <v>0.2314024020207064</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.07603337016459866</v>
+        <v>0.07459877827470041</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1765866956459811</v>
+        <v>0.1784866956459811</v>
       </c>
       <c r="C55">
-        <v>-15.65668685803094</v>
+        <v>-18.58149530145441</v>
       </c>
       <c r="D55">
-        <v>41.70611314196907</v>
+        <v>41.10890469854559</v>
       </c>
       <c r="E55">
-        <v>122.3028</v>
+        <v>124.6304</v>
       </c>
       <c r="F55">
-        <v>123.3628</v>
+        <v>125.6904</v>
       </c>
       <c r="G55">
         <v>66</v>
@@ -5785,37 +5785,37 @@
         <v>2.17</v>
       </c>
       <c r="M55">
-        <v>29.08894824</v>
+        <v>29.63779632</v>
       </c>
       <c r="N55">
-        <v>-26.91894824000001</v>
+        <v>-27.46779632</v>
       </c>
       <c r="O55">
-        <v>-6.729737060000001</v>
+        <v>-6.866949079999999</v>
       </c>
       <c r="P55">
-        <v>-20.18921118</v>
+        <v>-20.60084724</v>
       </c>
       <c r="Q55">
-        <v>-19.04921118</v>
+        <v>-19.46084724</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1147732395212908</v>
+        <v>0.1162726577717536</v>
       </c>
       <c r="T55">
-        <v>1.382476160492971</v>
+        <v>1.412529990068905</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.01864969456867513</v>
+        <v>0.0183043298544404</v>
       </c>
       <c r="W55">
-        <v>0.2314024020207064</v>
+        <v>0.231483839020323</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.07459877827470041</v>
+        <v>0.07321731941776166</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1784866956459811</v>
+        <v>0.1803866956459811</v>
       </c>
       <c r="C56">
-        <v>-18.58149530145441</v>
+        <v>-21.48944181009216</v>
       </c>
       <c r="D56">
-        <v>41.10890469854559</v>
+        <v>40.52855818990784</v>
       </c>
       <c r="E56">
-        <v>124.6304</v>
+        <v>126.958</v>
       </c>
       <c r="F56">
-        <v>125.6904</v>
+        <v>128.018</v>
       </c>
       <c r="G56">
         <v>66</v>
@@ -5867,37 +5867,37 @@
         <v>2.17</v>
       </c>
       <c r="M56">
-        <v>29.63779632</v>
+        <v>30.1866444</v>
       </c>
       <c r="N56">
-        <v>-27.46779632</v>
+        <v>-28.0166444</v>
       </c>
       <c r="O56">
-        <v>-6.866949079999999</v>
+        <v>-7.004161100000001</v>
       </c>
       <c r="P56">
-        <v>-20.60084724</v>
+        <v>-21.0124833</v>
       </c>
       <c r="Q56">
-        <v>-19.46084724</v>
+        <v>-19.8724833</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1162726577717536</v>
+        <v>0.1178387168333482</v>
       </c>
       <c r="T56">
-        <v>1.412529990068905</v>
+        <v>1.44391954540377</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.0183043298544404</v>
+        <v>0.01797152385708694</v>
       </c>
       <c r="W56">
-        <v>0.231483839020323</v>
+        <v>0.2315623146744989</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.07321731941776166</v>
+        <v>0.07188609542834767</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1803866956459811</v>
+        <v>0.1822866956459811</v>
       </c>
       <c r="C57">
-        <v>-21.48944181009216</v>
+        <v>-24.38123057732969</v>
       </c>
       <c r="D57">
-        <v>40.52855818990784</v>
+        <v>39.96436942267034</v>
       </c>
       <c r="E57">
-        <v>126.958</v>
+        <v>129.2856</v>
       </c>
       <c r="F57">
-        <v>128.018</v>
+        <v>130.3456</v>
       </c>
       <c r="G57">
         <v>66</v>
@@ -5949,37 +5949,37 @@
         <v>2.17</v>
       </c>
       <c r="M57">
-        <v>30.1866444</v>
+        <v>30.73549248</v>
       </c>
       <c r="N57">
-        <v>-28.0166444</v>
+        <v>-28.56549248</v>
       </c>
       <c r="O57">
-        <v>-7.004161100000001</v>
+        <v>-7.141373120000001</v>
       </c>
       <c r="P57">
-        <v>-21.0124833</v>
+        <v>-21.42411936</v>
       </c>
       <c r="Q57">
-        <v>-19.8724833</v>
+        <v>-20.28411936</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1178387168333482</v>
+        <v>0.1194759603977425</v>
       </c>
       <c r="T57">
-        <v>1.44391954540377</v>
+        <v>1.476735898708401</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.01797152385708694</v>
+        <v>0.01765060378821039</v>
       </c>
       <c r="W57">
-        <v>0.2315623146744989</v>
+        <v>0.23163798762674</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.07188609542834767</v>
+        <v>0.0706024151528416</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1822866956459811</v>
+        <v>0.1841866956459811</v>
       </c>
       <c r="C58">
-        <v>-24.38123057732969</v>
+        <v>-27.25752712325574</v>
       </c>
       <c r="D58">
-        <v>39.96436942267034</v>
+        <v>39.41567287674427</v>
       </c>
       <c r="E58">
-        <v>129.2856</v>
+        <v>131.6132</v>
       </c>
       <c r="F58">
-        <v>130.3456</v>
+        <v>132.6732</v>
       </c>
       <c r="G58">
         <v>66</v>
@@ -6031,37 +6031,37 @@
         <v>2.17</v>
       </c>
       <c r="M58">
-        <v>30.73549248</v>
+        <v>31.28434056</v>
       </c>
       <c r="N58">
-        <v>-28.56549248</v>
+        <v>-29.11434056</v>
       </c>
       <c r="O58">
-        <v>-7.141373120000001</v>
+        <v>-7.278585140000001</v>
       </c>
       <c r="P58">
-        <v>-21.42411936</v>
+        <v>-21.83575542</v>
       </c>
       <c r="Q58">
-        <v>-20.28411936</v>
+        <v>-20.69575542</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1194759603977425</v>
+        <v>0.1211893548255969</v>
       </c>
       <c r="T58">
-        <v>1.476735898708401</v>
+        <v>1.511078594027201</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.01765060378821039</v>
+        <v>0.01734094407262775</v>
       </c>
       <c r="W58">
-        <v>0.23163798762674</v>
+        <v>0.2317110053876744</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.0706024151528416</v>
+        <v>0.06936377629051105</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1841866956459811</v>
+        <v>0.1860866956459811</v>
       </c>
       <c r="C59">
-        <v>-27.25752712325574</v>
+        <v>-30.11896091355899</v>
       </c>
       <c r="D59">
-        <v>39.41567287674427</v>
+        <v>38.881839086441</v>
       </c>
       <c r="E59">
-        <v>131.6132</v>
+        <v>133.9408</v>
       </c>
       <c r="F59">
-        <v>132.6732</v>
+        <v>135.0008</v>
       </c>
       <c r="G59">
         <v>66</v>
@@ -6113,37 +6113,37 @@
         <v>2.17</v>
       </c>
       <c r="M59">
-        <v>31.28434056</v>
+        <v>31.83318864</v>
       </c>
       <c r="N59">
-        <v>-29.11434056</v>
+        <v>-29.66318864</v>
       </c>
       <c r="O59">
-        <v>-7.278585140000001</v>
+        <v>-7.41579716</v>
       </c>
       <c r="P59">
-        <v>-21.83575542</v>
+        <v>-22.24739148</v>
       </c>
       <c r="Q59">
-        <v>-20.69575542</v>
+        <v>-21.10739148</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1211893548255969</v>
+        <v>0.1229843394643016</v>
       </c>
       <c r="T59">
-        <v>1.511078594027201</v>
+        <v>1.547056655789754</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01734094407262775</v>
+        <v>0.0170419622782721</v>
       </c>
       <c r="W59">
-        <v>0.2317110053876744</v>
+        <v>0.2317815052947834</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.06936377629051105</v>
+        <v>0.06816784911308837</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1860866956459811</v>
+        <v>0.1879866956459811</v>
       </c>
       <c r="C60">
-        <v>-30.11896091355899</v>
+        <v>-32.96612776845078</v>
       </c>
       <c r="D60">
-        <v>38.881839086441</v>
+        <v>38.36227223154922</v>
       </c>
       <c r="E60">
-        <v>133.9408</v>
+        <v>136.2684</v>
       </c>
       <c r="F60">
-        <v>135.0008</v>
+        <v>137.3284</v>
       </c>
       <c r="G60">
         <v>66</v>
@@ -6195,37 +6195,37 @@
         <v>2.17</v>
       </c>
       <c r="M60">
-        <v>31.83318864</v>
+        <v>32.38203672</v>
       </c>
       <c r="N60">
-        <v>-29.66318864</v>
+        <v>-30.21203671999999</v>
       </c>
       <c r="O60">
-        <v>-7.41579716</v>
+        <v>-7.553009179999998</v>
       </c>
       <c r="P60">
-        <v>-22.24739148</v>
+        <v>-22.65902754</v>
       </c>
       <c r="Q60">
-        <v>-21.10739148</v>
+        <v>-21.51902754</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1229843394643016</v>
+        <v>0.1248668843292846</v>
       </c>
       <c r="T60">
-        <v>1.547056655789753</v>
+        <v>1.584789744955357</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0170419622782721</v>
+        <v>0.01675311545999631</v>
       </c>
       <c r="W60">
-        <v>0.2317815052947834</v>
+        <v>0.2318496153745329</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.06816784911308837</v>
+        <v>0.06701246183998533</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1879866956459811</v>
+        <v>0.1898866956459811</v>
       </c>
       <c r="C61">
-        <v>-32.96612776845078</v>
+        <v>-35.79959208099652</v>
       </c>
       <c r="D61">
-        <v>38.36227223154922</v>
+        <v>37.85640791900346</v>
       </c>
       <c r="E61">
-        <v>136.2684</v>
+        <v>138.596</v>
       </c>
       <c r="F61">
-        <v>137.3284</v>
+        <v>139.656</v>
       </c>
       <c r="G61">
         <v>66</v>
@@ -6277,37 +6277,37 @@
         <v>2.17</v>
       </c>
       <c r="M61">
-        <v>32.38203672</v>
+        <v>32.93088479999999</v>
       </c>
       <c r="N61">
-        <v>-30.21203671999999</v>
+        <v>-30.76088479999999</v>
       </c>
       <c r="O61">
-        <v>-7.553009179999998</v>
+        <v>-7.690221199999998</v>
       </c>
       <c r="P61">
-        <v>-22.65902754</v>
+        <v>-23.0706636</v>
       </c>
       <c r="Q61">
-        <v>-21.51902754</v>
+        <v>-21.9306636</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1248668843292846</v>
+        <v>0.1268435564375167</v>
       </c>
       <c r="T61">
-        <v>1.584789744955357</v>
+        <v>1.624409488579241</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.01675311545999631</v>
+        <v>0.01647389686899637</v>
       </c>
       <c r="W61">
-        <v>0.2318496153745329</v>
+        <v>0.2319154551182907</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.06701246183998533</v>
+        <v>0.06589558747598556</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1898866956459811</v>
+        <v>0.1917866956459811</v>
       </c>
       <c r="C62">
-        <v>-35.79959208099652</v>
+        <v>-38.6198888622192</v>
       </c>
       <c r="D62">
-        <v>37.85640791900346</v>
+        <v>37.3637111377808</v>
       </c>
       <c r="E62">
-        <v>138.596</v>
+        <v>140.9236</v>
       </c>
       <c r="F62">
-        <v>139.656</v>
+        <v>141.9836</v>
       </c>
       <c r="G62">
         <v>66</v>
@@ -6359,37 +6359,37 @@
         <v>2.17</v>
       </c>
       <c r="M62">
-        <v>32.93088479999999</v>
+        <v>33.47973288</v>
       </c>
       <c r="N62">
-        <v>-30.76088479999999</v>
+        <v>-31.30973288</v>
       </c>
       <c r="O62">
-        <v>-7.690221199999998</v>
+        <v>-7.82743322</v>
       </c>
       <c r="P62">
-        <v>-23.0706636</v>
+        <v>-23.48229966</v>
       </c>
       <c r="Q62">
-        <v>-21.9306636</v>
+        <v>-22.34229966</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1268435564375167</v>
+        <v>0.128921596346171</v>
       </c>
       <c r="T62">
-        <v>1.624409488579241</v>
+        <v>1.666061013927427</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.01647389686899637</v>
+        <v>0.01620383298589806</v>
       </c>
       <c r="W62">
-        <v>0.2319154551182907</v>
+        <v>0.2319791361819252</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.06589558747598556</v>
+        <v>0.06481533194359235</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1917866956459811</v>
+        <v>0.1936866956459811</v>
       </c>
       <c r="C63">
-        <v>-38.6198888622192</v>
+        <v>-41.42752562855364</v>
       </c>
       <c r="D63">
-        <v>37.3637111377808</v>
+        <v>36.88367437144635</v>
       </c>
       <c r="E63">
-        <v>140.9236</v>
+        <v>143.2512</v>
       </c>
       <c r="F63">
-        <v>141.9836</v>
+        <v>144.3112</v>
       </c>
       <c r="G63">
         <v>66</v>
@@ -6441,37 +6441,37 @@
         <v>2.17</v>
       </c>
       <c r="M63">
-        <v>33.47973288</v>
+        <v>34.02858096</v>
       </c>
       <c r="N63">
-        <v>-31.30973288</v>
+        <v>-31.85858096</v>
       </c>
       <c r="O63">
-        <v>-7.82743322</v>
+        <v>-7.964645239999999</v>
       </c>
       <c r="P63">
-        <v>-23.48229966</v>
+        <v>-23.89393572</v>
       </c>
       <c r="Q63">
-        <v>-22.34229966</v>
+        <v>-22.75393572</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.128921596346171</v>
+        <v>0.1311090067763334</v>
       </c>
       <c r="T63">
-        <v>1.666061013927427</v>
+        <v>1.709904724820254</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01620383298589806</v>
+        <v>0.01594248084096422</v>
       </c>
       <c r="W63">
-        <v>0.2319791361819252</v>
+        <v>0.2320407630177006</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.06481533194359235</v>
+        <v>0.0637699233638569</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1936866956459811</v>
+        <v>0.1955866956459811</v>
       </c>
       <c r="C64">
-        <v>-41.42752562855364</v>
+        <v>-44.22298414565039</v>
       </c>
       <c r="D64">
-        <v>36.88367437144635</v>
+        <v>36.41581585434962</v>
       </c>
       <c r="E64">
-        <v>143.2512</v>
+        <v>145.5788</v>
       </c>
       <c r="F64">
-        <v>144.3112</v>
+        <v>146.6388</v>
       </c>
       <c r="G64">
         <v>66</v>
@@ -6523,37 +6523,37 @@
         <v>2.17</v>
       </c>
       <c r="M64">
-        <v>34.02858096</v>
+        <v>34.57742904000001</v>
       </c>
       <c r="N64">
-        <v>-31.85858096</v>
+        <v>-32.40742904</v>
       </c>
       <c r="O64">
-        <v>-7.964645239999999</v>
+        <v>-8.101857260000001</v>
       </c>
       <c r="P64">
-        <v>-23.89393572</v>
+        <v>-24.30557178</v>
       </c>
       <c r="Q64">
-        <v>-22.75393572</v>
+        <v>-23.16557178</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1311090067763334</v>
+        <v>0.1334146556081262</v>
       </c>
       <c r="T64">
-        <v>1.709904724820254</v>
+        <v>1.756118366031612</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.01594248084096422</v>
+        <v>0.01568942558952035</v>
       </c>
       <c r="W64">
-        <v>0.2320407630177006</v>
+        <v>0.2321004334459911</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.0637699233638569</v>
+        <v>0.06275770235808142</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1955866956459811</v>
+        <v>0.1974866956459811</v>
       </c>
       <c r="C65">
-        <v>-44.22298414565039</v>
+        <v>-47.00672204112372</v>
       </c>
       <c r="D65">
-        <v>36.41581585434962</v>
+        <v>35.95967795887627</v>
       </c>
       <c r="E65">
-        <v>145.5788</v>
+        <v>147.9064</v>
       </c>
       <c r="F65">
-        <v>146.6388</v>
+        <v>148.9664</v>
       </c>
       <c r="G65">
         <v>66</v>
@@ -6605,37 +6605,37 @@
         <v>2.17</v>
       </c>
       <c r="M65">
-        <v>34.57742904000001</v>
+        <v>35.12627712</v>
       </c>
       <c r="N65">
-        <v>-32.40742904</v>
+        <v>-32.95627712</v>
       </c>
       <c r="O65">
-        <v>-8.101857260000001</v>
+        <v>-8.239069279999999</v>
       </c>
       <c r="P65">
-        <v>-24.30557178</v>
+        <v>-24.71720784</v>
       </c>
       <c r="Q65">
-        <v>-23.16557178</v>
+        <v>-23.57720784</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1334146556081262</v>
+        <v>0.1358483960416852</v>
       </c>
       <c r="T65">
-        <v>1.756118366031612</v>
+        <v>1.804899431754712</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01568942558952035</v>
+        <v>0.01544427831468409</v>
       </c>
       <c r="W65">
-        <v>0.2321004334459911</v>
+        <v>0.2321582391733975</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.06275770235808142</v>
+        <v>0.06177711325873647</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1974866956459811</v>
+        <v>0.1993866956459811</v>
       </c>
       <c r="C66">
-        <v>-47.00672204112372</v>
+        <v>-49.77917429759361</v>
       </c>
       <c r="D66">
-        <v>35.95967795887627</v>
+        <v>35.51482570240641</v>
       </c>
       <c r="E66">
-        <v>147.9064</v>
+        <v>150.234</v>
       </c>
       <c r="F66">
-        <v>148.9664</v>
+        <v>151.294</v>
       </c>
       <c r="G66">
         <v>66</v>
@@ -6687,37 +6687,37 @@
         <v>2.17</v>
       </c>
       <c r="M66">
-        <v>35.12627712</v>
+        <v>35.6751252</v>
       </c>
       <c r="N66">
-        <v>-32.95627712</v>
+        <v>-33.5051252</v>
       </c>
       <c r="O66">
-        <v>-8.239069279999999</v>
+        <v>-8.3762813</v>
       </c>
       <c r="P66">
-        <v>-24.71720784</v>
+        <v>-25.1288439</v>
       </c>
       <c r="Q66">
-        <v>-23.57720784</v>
+        <v>-23.9888439</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1358483960416852</v>
+        <v>0.1384212073571619</v>
       </c>
       <c r="T66">
-        <v>1.804899431754712</v>
+        <v>1.856467986947704</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01544427831468409</v>
+        <v>0.01520667403291972</v>
       </c>
       <c r="W66">
-        <v>0.2321582391733975</v>
+        <v>0.2322142662630375</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.06177711325873647</v>
+        <v>0.0608266961316789</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1993866956459811</v>
+        <v>0.2012866956459811</v>
       </c>
       <c r="C67">
-        <v>-49.77917429759361</v>
+        <v>-52.54075463626003</v>
       </c>
       <c r="D67">
-        <v>35.51482570240641</v>
+        <v>35.08084536373996</v>
       </c>
       <c r="E67">
-        <v>150.234</v>
+        <v>152.5616</v>
       </c>
       <c r="F67">
-        <v>151.294</v>
+        <v>153.6216</v>
       </c>
       <c r="G67">
         <v>66</v>
@@ -6769,37 +6769,37 @@
         <v>2.17</v>
       </c>
       <c r="M67">
-        <v>35.6751252</v>
+        <v>36.22397328</v>
       </c>
       <c r="N67">
-        <v>-33.5051252</v>
+        <v>-34.05397328</v>
       </c>
       <c r="O67">
-        <v>-8.3762813</v>
+        <v>-8.51349332</v>
       </c>
       <c r="P67">
-        <v>-25.1288439</v>
+        <v>-25.54047996</v>
       </c>
       <c r="Q67">
-        <v>-23.9888439</v>
+        <v>-24.40047996</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1384212073571619</v>
+        <v>0.1411453605147255</v>
       </c>
       <c r="T67">
-        <v>1.856467986947704</v>
+        <v>1.911069986563813</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01520667403291972</v>
+        <v>0.01497626988090578</v>
       </c>
       <c r="W67">
-        <v>0.2322142662630375</v>
+        <v>0.2322685955620824</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.0608266961316789</v>
+        <v>0.05990507952362323</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2012866956459811</v>
+        <v>0.2031866956459811</v>
       </c>
       <c r="C68">
-        <v>-52.54075463626003</v>
+        <v>-55.29185680026147</v>
       </c>
       <c r="D68">
-        <v>35.08084536373996</v>
+        <v>34.65734319973852</v>
       </c>
       <c r="E68">
-        <v>152.5616</v>
+        <v>154.8892</v>
       </c>
       <c r="F68">
-        <v>153.6216</v>
+        <v>155.9492</v>
       </c>
       <c r="G68">
         <v>66</v>
@@ -6851,37 +6851,37 @@
         <v>2.17</v>
       </c>
       <c r="M68">
-        <v>36.22397328</v>
+        <v>36.77282136</v>
       </c>
       <c r="N68">
-        <v>-34.05397328</v>
+        <v>-34.60282136</v>
       </c>
       <c r="O68">
-        <v>-8.51349332</v>
+        <v>-8.65070534</v>
       </c>
       <c r="P68">
-        <v>-25.54047996</v>
+        <v>-25.95211602</v>
       </c>
       <c r="Q68">
-        <v>-24.40047996</v>
+        <v>-24.81211602</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1411453605147255</v>
+        <v>0.1440346138636566</v>
       </c>
       <c r="T68">
-        <v>1.911069986563813</v>
+        <v>1.968981198277868</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01497626988090578</v>
+        <v>0.01475274346477286</v>
       </c>
       <c r="W68">
-        <v>0.2322685955620824</v>
+        <v>0.2323213030910066</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.05990507952362323</v>
+        <v>0.05901097385909149</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2031866956459811</v>
+        <v>0.2050866956459811</v>
       </c>
       <c r="C69">
-        <v>-55.29185680026147</v>
+        <v>-58.03285574618386</v>
       </c>
       <c r="D69">
-        <v>34.65734319973852</v>
+        <v>34.24394425381615</v>
       </c>
       <c r="E69">
-        <v>154.8892</v>
+        <v>157.2168</v>
       </c>
       <c r="F69">
-        <v>155.9492</v>
+        <v>158.2768</v>
       </c>
       <c r="G69">
         <v>66</v>
@@ -6933,37 +6933,37 @@
         <v>2.17</v>
       </c>
       <c r="M69">
-        <v>36.77282136</v>
+        <v>37.32166944</v>
       </c>
       <c r="N69">
-        <v>-34.60282136</v>
+        <v>-35.15166944</v>
       </c>
       <c r="O69">
-        <v>-8.65070534</v>
+        <v>-8.78791736</v>
       </c>
       <c r="P69">
-        <v>-25.95211602</v>
+        <v>-26.36375208</v>
       </c>
       <c r="Q69">
-        <v>-24.81211602</v>
+        <v>-25.22375208</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1440346138636566</v>
+        <v>0.1471044455468959</v>
       </c>
       <c r="T69">
-        <v>1.968981198277868</v>
+        <v>2.030511860724052</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01475274346477286</v>
+        <v>0.01453579135499679</v>
       </c>
       <c r="W69">
-        <v>0.2323213030910066</v>
+        <v>0.2323724603984918</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.05901097385909149</v>
+        <v>0.05814316541998721</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2050866956459811</v>
+        <v>0.2069866956459811</v>
       </c>
       <c r="C70">
-        <v>-58.03285574618386</v>
+        <v>-60.76410875130001</v>
       </c>
       <c r="D70">
-        <v>34.24394425381615</v>
+        <v>33.84029124869998</v>
       </c>
       <c r="E70">
-        <v>157.2168</v>
+        <v>159.5444</v>
       </c>
       <c r="F70">
-        <v>158.2768</v>
+        <v>160.6044</v>
       </c>
       <c r="G70">
         <v>66</v>
@@ -7015,37 +7015,37 @@
         <v>2.17</v>
       </c>
       <c r="M70">
-        <v>37.32166944</v>
+        <v>37.87051752</v>
       </c>
       <c r="N70">
-        <v>-35.15166944</v>
+        <v>-35.70051752</v>
       </c>
       <c r="O70">
-        <v>-8.78791736</v>
+        <v>-8.92512938</v>
       </c>
       <c r="P70">
-        <v>-26.36375208</v>
+        <v>-26.77538814</v>
       </c>
       <c r="Q70">
-        <v>-25.22375208</v>
+        <v>-25.63538814</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1471044455468959</v>
+        <v>0.1503723308871183</v>
       </c>
       <c r="T70">
-        <v>2.030511860724052</v>
+        <v>2.096012243328053</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01453579135499679</v>
+        <v>0.01432512771217075</v>
       </c>
       <c r="W70">
-        <v>0.2323724603984918</v>
+        <v>0.2324221348854701</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.05814316541998721</v>
+        <v>0.05730051084868304</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2069866956459811</v>
+        <v>0.2088866956459811</v>
       </c>
       <c r="C71">
-        <v>-60.76410875130001</v>
+        <v>-63.48595644341162</v>
       </c>
       <c r="D71">
-        <v>33.84029124869998</v>
+        <v>33.44604355658839</v>
       </c>
       <c r="E71">
-        <v>159.5444</v>
+        <v>161.872</v>
       </c>
       <c r="F71">
-        <v>160.6044</v>
+        <v>162.932</v>
       </c>
       <c r="G71">
         <v>66</v>
@@ -7097,37 +7097,37 @@
         <v>2.17</v>
       </c>
       <c r="M71">
-        <v>37.87051752</v>
+        <v>38.41936560000001</v>
       </c>
       <c r="N71">
-        <v>-35.70051752</v>
+        <v>-36.2493656</v>
       </c>
       <c r="O71">
-        <v>-8.92512938</v>
+        <v>-9.062341400000001</v>
       </c>
       <c r="P71">
-        <v>-26.77538814</v>
+        <v>-27.1870242</v>
       </c>
       <c r="Q71">
-        <v>-25.63538814</v>
+        <v>-26.0470242</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1503723308871183</v>
+        <v>0.1538580752500223</v>
       </c>
       <c r="T71">
-        <v>2.096012243328053</v>
+        <v>2.165879318105655</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01432512771217075</v>
+        <v>0.01412048303056831</v>
       </c>
       <c r="W71">
-        <v>0.2324221348854701</v>
+        <v>0.232470390101392</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.05730051084868304</v>
+        <v>0.05648193212227326</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2088866956459811</v>
+        <v>0.2107866956459811</v>
       </c>
       <c r="C72">
-        <v>-63.48595644341162</v>
+        <v>-66.19872375953187</v>
       </c>
       <c r="D72">
-        <v>33.44604355658839</v>
+        <v>33.06087624046813</v>
       </c>
       <c r="E72">
-        <v>161.872</v>
+        <v>164.1996</v>
       </c>
       <c r="F72">
-        <v>162.932</v>
+        <v>165.2596</v>
       </c>
       <c r="G72">
         <v>66</v>
@@ -7179,37 +7179,37 @@
         <v>2.17</v>
       </c>
       <c r="M72">
-        <v>38.41936560000001</v>
+        <v>38.96821368000001</v>
       </c>
       <c r="N72">
-        <v>-36.2493656</v>
+        <v>-36.79821368</v>
       </c>
       <c r="O72">
-        <v>-9.062341400000001</v>
+        <v>-9.199553420000001</v>
       </c>
       <c r="P72">
-        <v>-27.1870242</v>
+        <v>-27.59866026</v>
       </c>
       <c r="Q72">
-        <v>-26.0470242</v>
+        <v>-26.45866026</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1538580752500223</v>
+        <v>0.1575842157758851</v>
       </c>
       <c r="T72">
-        <v>2.165879318105655</v>
+        <v>2.240564811833437</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01412048303056831</v>
+        <v>0.01392160298788425</v>
       </c>
       <c r="W72">
-        <v>0.232470390101392</v>
+        <v>0.2325172860154569</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.05648193212227326</v>
+        <v>0.05568641195153701</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2107866956459811</v>
+        <v>0.2126866956459811</v>
       </c>
       <c r="C73">
-        <v>-66.19872375953187</v>
+        <v>-68.90272083908187</v>
       </c>
       <c r="D73">
-        <v>33.0608762404681</v>
+        <v>32.68447916091814</v>
       </c>
       <c r="E73">
-        <v>164.1996</v>
+        <v>166.5272</v>
       </c>
       <c r="F73">
-        <v>165.2596</v>
+        <v>167.5872</v>
       </c>
       <c r="G73">
         <v>66</v>
@@ -7261,37 +7261,37 @@
         <v>2.17</v>
       </c>
       <c r="M73">
-        <v>38.96821368</v>
+        <v>39.51706176</v>
       </c>
       <c r="N73">
-        <v>-36.79821368</v>
+        <v>-37.34706176</v>
       </c>
       <c r="O73">
-        <v>-9.199553419999999</v>
+        <v>-9.336765439999999</v>
       </c>
       <c r="P73">
-        <v>-27.59866026</v>
+        <v>-28.01029631999999</v>
       </c>
       <c r="Q73">
-        <v>-26.45866025999999</v>
+        <v>-26.87029631999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1575842157758851</v>
+        <v>0.1615765091964524</v>
       </c>
       <c r="T73">
-        <v>2.240564811833436</v>
+        <v>2.32058498368463</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01392160298788425</v>
+        <v>0.0137282473908303</v>
       </c>
       <c r="W73">
-        <v>0.2325172860154569</v>
+        <v>0.2325628792652422</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.05568641195153701</v>
+        <v>0.05491298956332125</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2126866956459811</v>
+        <v>0.2145866956459811</v>
       </c>
       <c r="C74">
-        <v>-68.90272083908187</v>
+        <v>-71.59824385675849</v>
       </c>
       <c r="D74">
-        <v>32.68447916091814</v>
+        <v>32.3165561432415</v>
       </c>
       <c r="E74">
-        <v>166.5272</v>
+        <v>168.8548</v>
       </c>
       <c r="F74">
-        <v>167.5872</v>
+        <v>169.9148</v>
       </c>
       <c r="G74">
         <v>66</v>
@@ -7343,37 +7343,37 @@
         <v>2.17</v>
       </c>
       <c r="M74">
-        <v>39.51706176</v>
+        <v>40.06590984</v>
       </c>
       <c r="N74">
-        <v>-37.34706176</v>
+        <v>-37.89590983999999</v>
       </c>
       <c r="O74">
-        <v>-9.336765439999999</v>
+        <v>-9.473977459999999</v>
       </c>
       <c r="P74">
-        <v>-28.01029631999999</v>
+        <v>-28.42193237999999</v>
       </c>
       <c r="Q74">
-        <v>-26.87029631999999</v>
+        <v>-27.28193237999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1615765091964524</v>
+        <v>0.1658645280555802</v>
       </c>
       <c r="T74">
-        <v>2.32058498368463</v>
+        <v>2.406532575672949</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0137282473908303</v>
+        <v>0.01354018920739427</v>
       </c>
       <c r="W74">
-        <v>0.2325628792652422</v>
+        <v>0.2326072233848964</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.05491298956332125</v>
+        <v>0.05416075682957711</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2145866956459811</v>
+        <v>0.2164866956459811</v>
       </c>
       <c r="C75">
-        <v>-71.59824385675849</v>
+        <v>-74.28557579977716</v>
       </c>
       <c r="D75">
-        <v>32.3165561432415</v>
+        <v>31.95682420022284</v>
       </c>
       <c r="E75">
-        <v>168.8548</v>
+        <v>171.1824</v>
       </c>
       <c r="F75">
-        <v>169.9148</v>
+        <v>172.2424</v>
       </c>
       <c r="G75">
         <v>66</v>
@@ -7425,37 +7425,37 @@
         <v>2.17</v>
       </c>
       <c r="M75">
-        <v>40.06590984</v>
+        <v>40.61475792</v>
       </c>
       <c r="N75">
-        <v>-37.89590983999999</v>
+        <v>-38.44475792</v>
       </c>
       <c r="O75">
-        <v>-9.473977459999999</v>
+        <v>-9.61118948</v>
       </c>
       <c r="P75">
-        <v>-28.42193237999999</v>
+        <v>-28.83356844</v>
       </c>
       <c r="Q75">
-        <v>-27.28193237999999</v>
+        <v>-27.69356844</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1658645280555802</v>
+        <v>0.1704823945192564</v>
       </c>
       <c r="T75">
-        <v>2.406532575672949</v>
+        <v>2.49909152089114</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01354018920739427</v>
+        <v>0.01335721367756462</v>
       </c>
       <c r="W75">
-        <v>0.2326072233848964</v>
+        <v>0.2326503690148303</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.05416075682957711</v>
+        <v>0.05342885471025849</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2164866956459811</v>
+        <v>0.2183866956459811</v>
       </c>
       <c r="C76">
-        <v>-74.28557579977716</v>
+        <v>-76.96498719377342</v>
       </c>
       <c r="D76">
-        <v>31.95682420022284</v>
+        <v>31.60501280622656</v>
       </c>
       <c r="E76">
-        <v>171.1824</v>
+        <v>173.51</v>
       </c>
       <c r="F76">
-        <v>172.2424</v>
+        <v>174.57</v>
       </c>
       <c r="G76">
         <v>66</v>
@@ -7507,37 +7507,37 @@
         <v>2.17</v>
       </c>
       <c r="M76">
-        <v>40.61475792</v>
+        <v>41.163606</v>
       </c>
       <c r="N76">
-        <v>-38.44475792</v>
+        <v>-38.993606</v>
       </c>
       <c r="O76">
-        <v>-9.61118948</v>
+        <v>-9.7484015</v>
       </c>
       <c r="P76">
-        <v>-28.83356844</v>
+        <v>-29.2452045</v>
       </c>
       <c r="Q76">
-        <v>-27.69356844</v>
+        <v>-28.1052045</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1704823945192564</v>
+        <v>0.1754696903000267</v>
       </c>
       <c r="T76">
-        <v>2.49909152089114</v>
+        <v>2.599055181726786</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01335721367756462</v>
+        <v>0.01317911749519709</v>
       </c>
       <c r="W76">
-        <v>0.2326503690148303</v>
+        <v>0.2326923640946325</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.05342885471025849</v>
+        <v>0.05271646998078838</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2183866956459811</v>
+        <v>0.2202866956459811</v>
       </c>
       <c r="C77">
-        <v>-76.96498719377342</v>
+        <v>-79.63673678127931</v>
       </c>
       <c r="D77">
-        <v>31.60501280622656</v>
+        <v>31.26086321872067</v>
       </c>
       <c r="E77">
-        <v>173.51</v>
+        <v>175.8376</v>
       </c>
       <c r="F77">
-        <v>174.57</v>
+        <v>176.8976</v>
       </c>
       <c r="G77">
         <v>66</v>
@@ -7589,37 +7589,37 @@
         <v>2.17</v>
       </c>
       <c r="M77">
-        <v>41.163606</v>
+        <v>41.71245408</v>
       </c>
       <c r="N77">
-        <v>-38.993606</v>
+        <v>-39.54245408</v>
       </c>
       <c r="O77">
-        <v>-9.7484015</v>
+        <v>-9.88561352</v>
       </c>
       <c r="P77">
-        <v>-29.2452045</v>
+        <v>-29.65684056</v>
       </c>
       <c r="Q77">
-        <v>-28.1052045</v>
+        <v>-28.51684056</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1754696903000267</v>
+        <v>0.1808725940625278</v>
       </c>
       <c r="T77">
-        <v>2.599055181726786</v>
+        <v>2.707349147632069</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01317911749519709</v>
+        <v>0.01300570805447081</v>
       </c>
       <c r="W77">
-        <v>0.2326923640946325</v>
+        <v>0.2327332540407558</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.05271646998078838</v>
+        <v>0.05202283221788329</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2202866956459811</v>
+        <v>0.2221866956459811</v>
       </c>
       <c r="C78">
-        <v>-79.63673678127931</v>
+        <v>-82.30107215634854</v>
       </c>
       <c r="D78">
-        <v>31.26086321872067</v>
+        <v>30.92412784365147</v>
       </c>
       <c r="E78">
-        <v>175.8376</v>
+        <v>178.1652</v>
       </c>
       <c r="F78">
-        <v>176.8976</v>
+        <v>179.2252</v>
       </c>
       <c r="G78">
         <v>66</v>
@@ -7671,37 +7671,37 @@
         <v>2.17</v>
       </c>
       <c r="M78">
-        <v>41.71245408</v>
+        <v>42.26130216</v>
       </c>
       <c r="N78">
-        <v>-39.54245408</v>
+        <v>-40.09130216</v>
       </c>
       <c r="O78">
-        <v>-9.88561352</v>
+        <v>-10.02282554</v>
       </c>
       <c r="P78">
-        <v>-29.65684056</v>
+        <v>-30.06847662</v>
       </c>
       <c r="Q78">
-        <v>-28.51684056</v>
+        <v>-28.92847662</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1808725940625278</v>
+        <v>0.1867453155435073</v>
       </c>
       <c r="T78">
-        <v>2.707349147632069</v>
+        <v>2.825059980137811</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01300570805447081</v>
+        <v>0.0128368027550621</v>
       </c>
       <c r="W78">
-        <v>0.2327332540407558</v>
+        <v>0.2327730819103564</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.05202283221788329</v>
+        <v>0.05134721102024842</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2221866956459811</v>
+        <v>0.2240866956459811</v>
       </c>
       <c r="C79">
-        <v>-82.30107215634854</v>
+        <v>-84.95823035860278</v>
       </c>
       <c r="D79">
-        <v>30.92412784365147</v>
+        <v>30.59456964139721</v>
       </c>
       <c r="E79">
-        <v>178.1652</v>
+        <v>180.4928</v>
       </c>
       <c r="F79">
-        <v>179.2252</v>
+        <v>181.5528</v>
       </c>
       <c r="G79">
         <v>66</v>
@@ -7753,37 +7753,37 @@
         <v>2.17</v>
       </c>
       <c r="M79">
-        <v>42.26130216</v>
+        <v>42.81015024</v>
       </c>
       <c r="N79">
-        <v>-40.09130216</v>
+        <v>-40.64015024</v>
       </c>
       <c r="O79">
-        <v>-10.02282554</v>
+        <v>-10.16003756</v>
       </c>
       <c r="P79">
-        <v>-30.06847662</v>
+        <v>-30.48011268</v>
       </c>
       <c r="Q79">
-        <v>-28.92847662</v>
+        <v>-29.34011268</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1867453155435073</v>
+        <v>0.1931519207954849</v>
       </c>
       <c r="T79">
-        <v>2.825059980137811</v>
+        <v>2.953471797416803</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0128368027550621</v>
+        <v>0.01267222836076643</v>
       </c>
       <c r="W79">
-        <v>0.2327730819103564</v>
+        <v>0.2328118885525313</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.05134721102024842</v>
+        <v>0.05068891344306581</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2240866956459811</v>
+        <v>0.2259866956459811</v>
       </c>
       <c r="C80">
-        <v>-84.95823035860278</v>
+        <v>-87.60843842969402</v>
       </c>
       <c r="D80">
-        <v>30.59456964139721</v>
+        <v>30.27196157030599</v>
       </c>
       <c r="E80">
-        <v>180.4928</v>
+        <v>182.8204</v>
       </c>
       <c r="F80">
-        <v>181.5528</v>
+        <v>183.8804</v>
       </c>
       <c r="G80">
         <v>66</v>
@@ -7835,37 +7835,37 @@
         <v>2.17</v>
       </c>
       <c r="M80">
-        <v>42.81015024</v>
+        <v>43.35899832</v>
       </c>
       <c r="N80">
-        <v>-40.64015024</v>
+        <v>-41.18899832</v>
       </c>
       <c r="O80">
-        <v>-10.16003756</v>
+        <v>-10.29724958</v>
       </c>
       <c r="P80">
-        <v>-30.48011268</v>
+        <v>-30.89174874</v>
       </c>
       <c r="Q80">
-        <v>-29.34011268</v>
+        <v>-29.75174874</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1931519207954849</v>
+        <v>0.2001686789286032</v>
       </c>
       <c r="T80">
-        <v>2.953471797416803</v>
+        <v>3.094113311579507</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01267222836076643</v>
+        <v>0.01251182040683268</v>
       </c>
       <c r="W80">
-        <v>0.2328118885525313</v>
+        <v>0.2328497127480689</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.05068891344306581</v>
+        <v>0.05004728162733074</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2259866956459811</v>
+        <v>0.2278866956459811</v>
       </c>
       <c r="C81">
-        <v>-87.60843842969402</v>
+        <v>-90.2519139349281</v>
       </c>
       <c r="D81">
-        <v>30.27196157030599</v>
+        <v>29.9560860650719</v>
       </c>
       <c r="E81">
-        <v>182.8204</v>
+        <v>185.148</v>
       </c>
       <c r="F81">
-        <v>183.8804</v>
+        <v>186.208</v>
       </c>
       <c r="G81">
         <v>66</v>
@@ -7917,37 +7917,37 @@
         <v>2.17</v>
       </c>
       <c r="M81">
-        <v>43.35899832</v>
+        <v>43.9078464</v>
       </c>
       <c r="N81">
-        <v>-41.18899832</v>
+        <v>-41.7378464</v>
       </c>
       <c r="O81">
-        <v>-10.29724958</v>
+        <v>-10.4344616</v>
       </c>
       <c r="P81">
-        <v>-30.89174874</v>
+        <v>-31.3033848</v>
       </c>
       <c r="Q81">
-        <v>-29.75174874</v>
+        <v>-30.1633848</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2001686789286032</v>
+        <v>0.2078871128750334</v>
       </c>
       <c r="T81">
-        <v>3.094113311579507</v>
+        <v>3.248818977158483</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01251182040683268</v>
+        <v>0.01235542265174727</v>
       </c>
       <c r="W81">
-        <v>0.2328497127480689</v>
+        <v>0.232886591338718</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.05004728162733074</v>
+        <v>0.04942169060698909</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2278866956459811</v>
+        <v>0.2297866956459811</v>
       </c>
       <c r="C82">
-        <v>-90.2519139349281</v>
+        <v>-92.88886545256804</v>
       </c>
       <c r="D82">
-        <v>29.9560860650719</v>
+        <v>29.64673454743197</v>
       </c>
       <c r="E82">
-        <v>185.148</v>
+        <v>187.4756</v>
       </c>
       <c r="F82">
-        <v>186.208</v>
+        <v>188.5356</v>
       </c>
       <c r="G82">
         <v>66</v>
@@ -7999,37 +7999,37 @@
         <v>2.17</v>
       </c>
       <c r="M82">
-        <v>43.9078464</v>
+        <v>44.45669448</v>
       </c>
       <c r="N82">
-        <v>-41.7378464</v>
+        <v>-42.28669448</v>
       </c>
       <c r="O82">
-        <v>-10.4344616</v>
+        <v>-10.57167362</v>
       </c>
       <c r="P82">
-        <v>-31.3033848</v>
+        <v>-31.71502086</v>
       </c>
       <c r="Q82">
-        <v>-30.1633848</v>
+        <v>-30.57502086</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2078871128750334</v>
+        <v>0.2164180135526668</v>
       </c>
       <c r="T82">
-        <v>3.248818977158483</v>
+        <v>3.419809449640509</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01235542265174727</v>
+        <v>0.01220288656962694</v>
       </c>
       <c r="W82">
-        <v>0.232886591338718</v>
+        <v>0.232922559346882</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.04942169060698909</v>
+        <v>0.04881154627850781</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2297866956459811</v>
+        <v>0.2316866956459811</v>
       </c>
       <c r="C83">
-        <v>-92.88886545256804</v>
+        <v>-95.51949303312924</v>
       </c>
       <c r="D83">
-        <v>29.64673454743197</v>
+        <v>29.34370696687077</v>
       </c>
       <c r="E83">
-        <v>187.4756</v>
+        <v>189.8032</v>
       </c>
       <c r="F83">
-        <v>188.5356</v>
+        <v>190.8632</v>
       </c>
       <c r="G83">
         <v>66</v>
@@ -8081,37 +8081,37 @@
         <v>2.17</v>
       </c>
       <c r="M83">
-        <v>44.45669448</v>
+        <v>45.00554256</v>
       </c>
       <c r="N83">
-        <v>-42.28669448</v>
+        <v>-42.83554256</v>
       </c>
       <c r="O83">
-        <v>-10.57167362</v>
+        <v>-10.70888564</v>
       </c>
       <c r="P83">
-        <v>-31.71502086</v>
+        <v>-32.12665692</v>
       </c>
       <c r="Q83">
-        <v>-30.57502086</v>
+        <v>-30.98665692</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2164180135526668</v>
+        <v>0.2258967920833705</v>
       </c>
       <c r="T83">
-        <v>3.419809449640509</v>
+        <v>3.609798863509426</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01220288656962694</v>
+        <v>0.01205407087975344</v>
       </c>
       <c r="W83">
-        <v>0.232922559346882</v>
+        <v>0.2329576500865542</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.04881154627850781</v>
+        <v>0.04821628351901375</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2316866956459811</v>
+        <v>0.2335866956459811</v>
       </c>
       <c r="C84">
-        <v>-95.51949303312924</v>
+        <v>-98.14398863079268</v>
       </c>
       <c r="D84">
-        <v>29.34370696687077</v>
+        <v>29.04681136920732</v>
       </c>
       <c r="E84">
-        <v>189.8032</v>
+        <v>192.1308</v>
       </c>
       <c r="F84">
-        <v>190.8632</v>
+        <v>193.1908</v>
       </c>
       <c r="G84">
         <v>66</v>
@@ -8163,37 +8163,37 @@
         <v>2.17</v>
       </c>
       <c r="M84">
-        <v>45.00554256</v>
+        <v>45.55439064</v>
       </c>
       <c r="N84">
-        <v>-42.83554256</v>
+        <v>-43.38439064</v>
       </c>
       <c r="O84">
-        <v>-10.70888564</v>
+        <v>-10.84609766</v>
       </c>
       <c r="P84">
-        <v>-32.12665692</v>
+        <v>-32.53829298</v>
       </c>
       <c r="Q84">
-        <v>-30.98665692</v>
+        <v>-31.39829298</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2258967920833705</v>
+        <v>0.2364907210294511</v>
       </c>
       <c r="T84">
-        <v>3.609798863509426</v>
+        <v>3.822139973127627</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01205407087975344</v>
+        <v>0.01190884111011785</v>
       </c>
       <c r="W84">
-        <v>0.2329576500865542</v>
+        <v>0.2329918952662342</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.04821628351901375</v>
+        <v>0.04763536444047145</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2335866956459811</v>
+        <v>0.2354866956459811</v>
       </c>
       <c r="C85">
-        <v>-98.14398863079268</v>
+        <v>-100.76253650889</v>
       </c>
       <c r="D85">
-        <v>29.04681136920732</v>
+        <v>28.75586349110999</v>
       </c>
       <c r="E85">
-        <v>192.1308</v>
+        <v>194.4584</v>
       </c>
       <c r="F85">
-        <v>193.1908</v>
+        <v>195.5184</v>
       </c>
       <c r="G85">
         <v>66</v>
@@ -8245,37 +8245,37 @@
         <v>2.17</v>
       </c>
       <c r="M85">
-        <v>45.55439064</v>
+        <v>46.10323872000001</v>
       </c>
       <c r="N85">
-        <v>-43.38439064</v>
+        <v>-43.93323872000001</v>
       </c>
       <c r="O85">
-        <v>-10.84609766</v>
+        <v>-10.98330968</v>
       </c>
       <c r="P85">
-        <v>-32.53829298</v>
+        <v>-32.94992904</v>
       </c>
       <c r="Q85">
-        <v>-31.39829298</v>
+        <v>-31.80992904</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2364907210294511</v>
+        <v>0.2484088910937919</v>
       </c>
       <c r="T85">
-        <v>3.822139973127627</v>
+        <v>4.061023721448105</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01190884111011785</v>
+        <v>0.01176706919214026</v>
       </c>
       <c r="W85">
-        <v>0.2329918952662342</v>
+        <v>0.2330253250844933</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.04763536444047145</v>
+        <v>0.04706827676856107</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2354866956459811</v>
+        <v>0.2373866956459811</v>
       </c>
       <c r="C86">
-        <v>-100.76253650889</v>
+        <v>-103.3753136212614</v>
       </c>
       <c r="D86">
-        <v>28.75586349110997</v>
+        <v>28.47068637873855</v>
       </c>
       <c r="E86">
-        <v>194.4584</v>
+        <v>196.786</v>
       </c>
       <c r="F86">
-        <v>195.5184</v>
+        <v>197.846</v>
       </c>
       <c r="G86">
         <v>66</v>
@@ -8327,37 +8327,37 @@
         <v>2.17</v>
       </c>
       <c r="M86">
-        <v>46.10323872</v>
+        <v>46.6520868</v>
       </c>
       <c r="N86">
-        <v>-43.93323872</v>
+        <v>-44.4820868</v>
       </c>
       <c r="O86">
-        <v>-10.98330968</v>
+        <v>-11.1205217</v>
       </c>
       <c r="P86">
-        <v>-32.94992904</v>
+        <v>-33.3615651</v>
       </c>
       <c r="Q86">
-        <v>-31.80992904</v>
+        <v>-32.2215651</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2484088910937917</v>
+        <v>0.2619161505000445</v>
       </c>
       <c r="T86">
-        <v>4.061023721448103</v>
+        <v>4.331758636211309</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01176706919214026</v>
+        <v>0.01162863308399743</v>
       </c>
       <c r="W86">
-        <v>0.2330253250844933</v>
+        <v>0.2330579683187934</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.04706827676856107</v>
+        <v>0.04651453233598979</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2373866956459811</v>
+        <v>0.239286695645981</v>
       </c>
       <c r="C87">
-        <v>-103.3753136212614</v>
+        <v>-105.9824899711443</v>
       </c>
       <c r="D87">
-        <v>28.47068637873855</v>
+        <v>28.19111002885566</v>
       </c>
       <c r="E87">
-        <v>196.786</v>
+        <v>199.1136</v>
       </c>
       <c r="F87">
-        <v>197.846</v>
+        <v>200.1736</v>
       </c>
       <c r="G87">
         <v>66</v>
@@ -8409,37 +8409,37 @@
         <v>2.17</v>
       </c>
       <c r="M87">
-        <v>46.6520868</v>
+        <v>47.20093488</v>
       </c>
       <c r="N87">
-        <v>-44.4820868</v>
+        <v>-45.03093488</v>
       </c>
       <c r="O87">
-        <v>-11.1205217</v>
+        <v>-11.25773372</v>
       </c>
       <c r="P87">
-        <v>-33.3615651</v>
+        <v>-33.77320116</v>
       </c>
       <c r="Q87">
-        <v>-32.2215651</v>
+        <v>-32.63320116</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2619161505000445</v>
+        <v>0.2773530183929048</v>
       </c>
       <c r="T87">
-        <v>4.331758636211309</v>
+        <v>4.64116996736926</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01162863308399743</v>
+        <v>0.01149341642023002</v>
       </c>
       <c r="W87">
-        <v>0.2330579683187934</v>
+        <v>0.2330898524081098</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.04651453233598979</v>
+        <v>0.04597366568092009</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.239286695645981</v>
+        <v>0.2411866956459811</v>
       </c>
       <c r="C88">
-        <v>-105.9824899711443</v>
+        <v>-108.584228949122</v>
       </c>
       <c r="D88">
-        <v>28.19111002885566</v>
+        <v>27.91697105087797</v>
       </c>
       <c r="E88">
-        <v>199.1136</v>
+        <v>201.4412</v>
       </c>
       <c r="F88">
-        <v>200.1736</v>
+        <v>202.5012</v>
       </c>
       <c r="G88">
         <v>66</v>
@@ -8491,37 +8491,37 @@
         <v>2.17</v>
       </c>
       <c r="M88">
-        <v>47.20093488</v>
+        <v>47.74978296</v>
       </c>
       <c r="N88">
-        <v>-45.03093488</v>
+        <v>-45.57978296</v>
       </c>
       <c r="O88">
-        <v>-11.25773372</v>
+        <v>-11.39494574</v>
       </c>
       <c r="P88">
-        <v>-33.77320116</v>
+        <v>-34.18483722</v>
       </c>
       <c r="Q88">
-        <v>-32.63320116</v>
+        <v>-33.04483722</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2773530183929048</v>
+        <v>0.2951647890385128</v>
       </c>
       <c r="T88">
-        <v>4.64116996736926</v>
+        <v>4.99818304178228</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01149341642023002</v>
+        <v>0.01136130818551473</v>
       </c>
       <c r="W88">
-        <v>0.2330898524081098</v>
+        <v>0.2331210035298556</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.04597366568092009</v>
+        <v>0.04544523274205903</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2411866956459811</v>
+        <v>0.2430866956459811</v>
       </c>
       <c r="C89">
-        <v>-108.584228949122</v>
+        <v>-111.1806876515449</v>
       </c>
       <c r="D89">
-        <v>27.91697105087797</v>
+        <v>27.64811234845514</v>
       </c>
       <c r="E89">
-        <v>201.4412</v>
+        <v>203.7688</v>
       </c>
       <c r="F89">
-        <v>202.5012</v>
+        <v>204.8288</v>
       </c>
       <c r="G89">
         <v>66</v>
@@ -8573,37 +8573,37 @@
         <v>2.17</v>
       </c>
       <c r="M89">
-        <v>47.74978296</v>
+        <v>48.29863104</v>
       </c>
       <c r="N89">
-        <v>-45.57978296</v>
+        <v>-46.12863104</v>
       </c>
       <c r="O89">
-        <v>-11.39494574</v>
+        <v>-11.53215776</v>
       </c>
       <c r="P89">
-        <v>-34.18483722</v>
+        <v>-34.59647328</v>
       </c>
       <c r="Q89">
-        <v>-33.04483722</v>
+        <v>-33.45647328</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2951647890385128</v>
+        <v>0.3159451881250556</v>
       </c>
       <c r="T89">
-        <v>4.99818304178228</v>
+        <v>5.414698295264137</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01136130818551473</v>
+        <v>0.01123220241067934</v>
       </c>
       <c r="W89">
-        <v>0.2331210035298556</v>
+        <v>0.2331514466715618</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.04544523274205903</v>
+        <v>0.04492880964271739</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2430866956459811</v>
+        <v>0.2449866956459811</v>
       </c>
       <c r="C90">
-        <v>-111.1806876515449</v>
+        <v>-113.772017180727</v>
       </c>
       <c r="D90">
-        <v>27.64811234845514</v>
+        <v>27.38438281927296</v>
       </c>
       <c r="E90">
-        <v>203.7688</v>
+        <v>206.0964</v>
       </c>
       <c r="F90">
-        <v>204.8288</v>
+        <v>207.1564</v>
       </c>
       <c r="G90">
         <v>66</v>
@@ -8655,37 +8655,37 @@
         <v>2.17</v>
       </c>
       <c r="M90">
-        <v>48.29863104</v>
+        <v>48.84747912</v>
       </c>
       <c r="N90">
-        <v>-46.12863104</v>
+        <v>-46.67747912</v>
       </c>
       <c r="O90">
-        <v>-11.53215776</v>
+        <v>-11.66936978</v>
       </c>
       <c r="P90">
-        <v>-34.59647328</v>
+        <v>-35.00810934</v>
       </c>
       <c r="Q90">
-        <v>-33.45647328</v>
+        <v>-33.86810934</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3159451881250556</v>
+        <v>0.3405038415909697</v>
       </c>
       <c r="T90">
-        <v>5.414698295264137</v>
+        <v>5.906943594833604</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01123220241067934</v>
+        <v>0.01110599788921103</v>
       </c>
       <c r="W90">
-        <v>0.2331514466715618</v>
+        <v>0.233181205697724</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.04492880964271739</v>
+        <v>0.04442399155684418</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2449866956459811</v>
+        <v>0.2468866956459811</v>
       </c>
       <c r="C91">
-        <v>-113.772017180727</v>
+        <v>-116.3583629281246</v>
       </c>
       <c r="D91">
-        <v>27.38438281927296</v>
+        <v>27.12563707187542</v>
       </c>
       <c r="E91">
-        <v>206.0964</v>
+        <v>208.424</v>
       </c>
       <c r="F91">
-        <v>207.1564</v>
+        <v>209.484</v>
       </c>
       <c r="G91">
         <v>66</v>
@@ -8737,37 +8737,37 @@
         <v>2.17</v>
       </c>
       <c r="M91">
-        <v>48.84747912</v>
+        <v>49.3963272</v>
       </c>
       <c r="N91">
-        <v>-46.67747912</v>
+        <v>-47.2263272</v>
       </c>
       <c r="O91">
-        <v>-11.66936978</v>
+        <v>-11.8065818</v>
       </c>
       <c r="P91">
-        <v>-35.00810934</v>
+        <v>-35.4197454</v>
       </c>
       <c r="Q91">
-        <v>-33.86810934</v>
+        <v>-34.2797454</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3405038415909697</v>
+        <v>0.3699742257500668</v>
       </c>
       <c r="T91">
-        <v>5.906943594833604</v>
+        <v>6.497637954316966</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01110599788921103</v>
+        <v>0.01098259791266424</v>
       </c>
       <c r="W91">
-        <v>0.233181205697724</v>
+        <v>0.2332103034121938</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.04442399155684418</v>
+        <v>0.04393039165065704</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2468866956459811</v>
+        <v>0.2487866956459811</v>
       </c>
       <c r="C92">
-        <v>-116.3583629281246</v>
+        <v>-118.9398648416098</v>
       </c>
       <c r="D92">
-        <v>27.12563707187542</v>
+        <v>26.8717351583902</v>
       </c>
       <c r="E92">
-        <v>208.424</v>
+        <v>210.7516</v>
       </c>
       <c r="F92">
-        <v>209.484</v>
+        <v>211.8116</v>
       </c>
       <c r="G92">
         <v>66</v>
@@ -8819,37 +8819,37 @@
         <v>2.17</v>
       </c>
       <c r="M92">
-        <v>49.3963272</v>
+        <v>49.94517528</v>
       </c>
       <c r="N92">
-        <v>-47.2263272</v>
+        <v>-47.77517528</v>
       </c>
       <c r="O92">
-        <v>-11.8065818</v>
+        <v>-11.94379382</v>
       </c>
       <c r="P92">
-        <v>-35.4197454</v>
+        <v>-35.83138146</v>
       </c>
       <c r="Q92">
-        <v>-34.2797454</v>
+        <v>-34.69138146</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3699742257500668</v>
+        <v>0.405993584166741</v>
       </c>
       <c r="T92">
-        <v>6.497637954316966</v>
+        <v>7.219597727018852</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01098259791266424</v>
+        <v>0.01086191002351409</v>
       </c>
       <c r="W92">
-        <v>0.2332103034121938</v>
+        <v>0.2332387616164554</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.04393039165065704</v>
+        <v>0.04344764009405633</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2487866956459811</v>
+        <v>0.2506866956459811</v>
       </c>
       <c r="C93">
-        <v>-118.9398648416098</v>
+        <v>-121.5166576778746</v>
       </c>
       <c r="D93">
-        <v>26.8717351583902</v>
+        <v>26.6225423221254</v>
       </c>
       <c r="E93">
-        <v>210.7516</v>
+        <v>213.0792</v>
       </c>
       <c r="F93">
-        <v>211.8116</v>
+        <v>214.1392</v>
       </c>
       <c r="G93">
         <v>66</v>
@@ -8901,37 +8901,37 @@
         <v>2.17</v>
       </c>
       <c r="M93">
-        <v>49.94517528</v>
+        <v>50.49402336</v>
       </c>
       <c r="N93">
-        <v>-47.77517528</v>
+        <v>-48.32402336</v>
       </c>
       <c r="O93">
-        <v>-11.94379382</v>
+        <v>-12.08100584</v>
       </c>
       <c r="P93">
-        <v>-35.83138146</v>
+        <v>-36.24301752</v>
       </c>
       <c r="Q93">
-        <v>-34.69138146</v>
+        <v>-35.10301751999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.405993584166741</v>
+        <v>0.4510177821875837</v>
       </c>
       <c r="T93">
-        <v>7.219597727018852</v>
+        <v>8.122047442896211</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01086191002351409</v>
+        <v>0.01074384578412806</v>
       </c>
       <c r="W93">
-        <v>0.2332387616164554</v>
+        <v>0.2332666011641026</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.04344764009405633</v>
+        <v>0.04297538313651228</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2506866956459811</v>
+        <v>0.2525866956459811</v>
       </c>
       <c r="C94">
-        <v>-121.5166576778746</v>
+        <v>-124.0888712409185</v>
       </c>
       <c r="D94">
-        <v>26.6225423221254</v>
+        <v>26.37792875908148</v>
       </c>
       <c r="E94">
-        <v>213.0792</v>
+        <v>215.4068</v>
       </c>
       <c r="F94">
-        <v>214.1392</v>
+        <v>216.4668</v>
       </c>
       <c r="G94">
         <v>66</v>
@@ -8983,37 +8983,37 @@
         <v>2.17</v>
       </c>
       <c r="M94">
-        <v>50.49402336</v>
+        <v>51.04287144000001</v>
       </c>
       <c r="N94">
-        <v>-48.32402336</v>
+        <v>-48.87287144</v>
       </c>
       <c r="O94">
-        <v>-12.08100584</v>
+        <v>-12.21821786</v>
       </c>
       <c r="P94">
-        <v>-36.24301752</v>
+        <v>-36.65465358</v>
       </c>
       <c r="Q94">
-        <v>-35.10301751999999</v>
+        <v>-35.51465358</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4510177821875837</v>
+        <v>0.5089060367858099</v>
       </c>
       <c r="T94">
-        <v>8.122047442896211</v>
+        <v>9.282339934738527</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01074384578412806</v>
+        <v>0.01062832056064282</v>
       </c>
       <c r="W94">
-        <v>0.2332666011641026</v>
+        <v>0.2332938420118005</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.04297538313651228</v>
+        <v>0.04251328224257134</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2525866956459811</v>
+        <v>0.2544866956459811</v>
       </c>
       <c r="C95">
-        <v>-124.0888712409185</v>
+        <v>-126.6566306075092</v>
       </c>
       <c r="D95">
-        <v>26.37792875908148</v>
+        <v>26.13776939249075</v>
       </c>
       <c r="E95">
-        <v>215.4068</v>
+        <v>217.7344</v>
       </c>
       <c r="F95">
-        <v>216.4668</v>
+        <v>218.7944</v>
       </c>
       <c r="G95">
         <v>66</v>
@@ -9065,37 +9065,37 @@
         <v>2.17</v>
       </c>
       <c r="M95">
-        <v>51.04287144000001</v>
+        <v>51.59171952</v>
       </c>
       <c r="N95">
-        <v>-48.87287144</v>
+        <v>-49.42171952</v>
       </c>
       <c r="O95">
-        <v>-12.21821786</v>
+        <v>-12.35542988</v>
       </c>
       <c r="P95">
-        <v>-36.65465358</v>
+        <v>-37.06628963999999</v>
       </c>
       <c r="Q95">
-        <v>-35.51465358</v>
+        <v>-35.92628963999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5089060367858099</v>
+        <v>0.5860903762501117</v>
       </c>
       <c r="T95">
-        <v>9.282339934738527</v>
+        <v>10.82939659052828</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01062832056064282</v>
+        <v>0.01051525332063598</v>
       </c>
       <c r="W95">
-        <v>0.2332938420118005</v>
+        <v>0.2333205032669941</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.04251328224257134</v>
+        <v>0.04206101328254397</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2544866956459811</v>
+        <v>0.2563866956459811</v>
       </c>
       <c r="C96">
-        <v>-126.6566306075092</v>
+        <v>-129.2200563404379</v>
       </c>
       <c r="D96">
-        <v>26.13776939249075</v>
+        <v>25.90194365956211</v>
       </c>
       <c r="E96">
-        <v>217.7344</v>
+        <v>220.062</v>
       </c>
       <c r="F96">
-        <v>218.7944</v>
+        <v>221.122</v>
       </c>
       <c r="G96">
         <v>66</v>
@@ -9147,37 +9147,37 @@
         <v>2.17</v>
       </c>
       <c r="M96">
-        <v>51.59171952</v>
+        <v>52.1405676</v>
       </c>
       <c r="N96">
-        <v>-49.42171952</v>
+        <v>-49.9705676</v>
       </c>
       <c r="O96">
-        <v>-12.35542988</v>
+        <v>-12.4926419</v>
       </c>
       <c r="P96">
-        <v>-37.06628963999999</v>
+        <v>-37.4779257</v>
       </c>
       <c r="Q96">
-        <v>-35.92628963999999</v>
+        <v>-36.3379257</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5860903762501117</v>
+        <v>0.6941484515001344</v>
       </c>
       <c r="T96">
-        <v>10.82939659052828</v>
+        <v>12.99527590863395</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01051525332063598</v>
+        <v>0.01040456644357665</v>
       </c>
       <c r="W96">
-        <v>0.2333205032669941</v>
+        <v>0.2333466032326046</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.04206101328254397</v>
+        <v>0.04161826577430661</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2563866956459811</v>
+        <v>0.2582866956459811</v>
       </c>
       <c r="C97">
-        <v>-129.2200563404379</v>
+        <v>-131.7792646903327</v>
       </c>
       <c r="D97">
-        <v>25.90194365956211</v>
+        <v>25.6703353096673</v>
       </c>
       <c r="E97">
-        <v>220.062</v>
+        <v>222.3896</v>
       </c>
       <c r="F97">
-        <v>221.122</v>
+        <v>223.4496</v>
       </c>
       <c r="G97">
         <v>66</v>
@@ -9229,37 +9229,37 @@
         <v>2.17</v>
       </c>
       <c r="M97">
-        <v>52.1405676</v>
+        <v>52.68941568</v>
       </c>
       <c r="N97">
-        <v>-49.9705676</v>
+        <v>-50.51941568</v>
       </c>
       <c r="O97">
-        <v>-12.4926419</v>
+        <v>-12.62985392</v>
       </c>
       <c r="P97">
-        <v>-37.4779257</v>
+        <v>-37.88956176</v>
       </c>
       <c r="Q97">
-        <v>-36.3379257</v>
+        <v>-36.74956176</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6941484515001344</v>
+        <v>0.8562355643751682</v>
       </c>
       <c r="T97">
-        <v>12.99527590863395</v>
+        <v>16.24409488579244</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01040456644357665</v>
+        <v>0.01029618554312273</v>
       </c>
       <c r="W97">
-        <v>0.2333466032326046</v>
+        <v>0.2333721594489317</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.04161826577430661</v>
+        <v>0.04118474217249091</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2582866956459811</v>
+        <v>0.2601866956459811</v>
       </c>
       <c r="C98">
-        <v>-131.7792646903327</v>
+        <v>-134.3343677867418</v>
       </c>
       <c r="D98">
-        <v>25.6703353096673</v>
+        <v>25.44283221325825</v>
       </c>
       <c r="E98">
-        <v>222.3896</v>
+        <v>224.7172</v>
       </c>
       <c r="F98">
-        <v>223.4496</v>
+        <v>225.7772</v>
       </c>
       <c r="G98">
         <v>66</v>
@@ -9311,37 +9311,37 @@
         <v>2.17</v>
       </c>
       <c r="M98">
-        <v>52.68941568</v>
+        <v>53.23826376</v>
       </c>
       <c r="N98">
-        <v>-50.51941567999999</v>
+        <v>-51.06826376</v>
       </c>
       <c r="O98">
-        <v>-12.62985392</v>
+        <v>-12.76706594</v>
       </c>
       <c r="P98">
-        <v>-37.88956175999999</v>
+        <v>-38.30119782</v>
       </c>
       <c r="Q98">
-        <v>-36.74956175999999</v>
+        <v>-37.16119782</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8562355643751662</v>
+        <v>1.126380752500222</v>
       </c>
       <c r="T98">
-        <v>16.2440948857924</v>
+        <v>21.65879318105653</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01029618554312273</v>
+        <v>0.01019003930041012</v>
       </c>
       <c r="W98">
-        <v>0.2333721594489317</v>
+        <v>0.2333971887329633</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.04118474217249091</v>
+        <v>0.0407601572016405</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2601866956459811</v>
+        <v>0.2620866956459811</v>
       </c>
       <c r="C99">
-        <v>-134.3343677867418</v>
+        <v>-136.8854738191438</v>
       </c>
       <c r="D99">
-        <v>25.44283221325825</v>
+        <v>25.21932618085616</v>
       </c>
       <c r="E99">
-        <v>224.7172</v>
+        <v>227.0448</v>
       </c>
       <c r="F99">
-        <v>225.7772</v>
+        <v>228.1048</v>
       </c>
       <c r="G99">
         <v>66</v>
@@ -9393,37 +9393,37 @@
         <v>2.17</v>
       </c>
       <c r="M99">
-        <v>53.23826376</v>
+        <v>53.78711184</v>
       </c>
       <c r="N99">
-        <v>-51.06826376</v>
+        <v>-51.61711184</v>
       </c>
       <c r="O99">
-        <v>-12.76706594</v>
+        <v>-12.90427796</v>
       </c>
       <c r="P99">
-        <v>-38.30119782</v>
+        <v>-38.71283388</v>
       </c>
       <c r="Q99">
-        <v>-37.16119782</v>
+        <v>-37.57283388</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.126380752500222</v>
+        <v>1.666671128750333</v>
       </c>
       <c r="T99">
-        <v>21.65879318105653</v>
+        <v>32.4881897715848</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01019003930041012</v>
+        <v>0.0100860593075488</v>
       </c>
       <c r="W99">
-        <v>0.2333971887329633</v>
+        <v>0.23342170721528</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.0407601572016405</v>
+        <v>0.0403442372301952</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2620866956459811</v>
+        <v>0.2639866956459811</v>
       </c>
       <c r="C100">
-        <v>-136.8854738191438</v>
+        <v>-139.4326872085018</v>
       </c>
       <c r="D100">
-        <v>25.21932618085616</v>
+        <v>24.99971279149819</v>
       </c>
       <c r="E100">
-        <v>227.0448</v>
+        <v>229.3724</v>
       </c>
       <c r="F100">
-        <v>228.1048</v>
+        <v>230.4324</v>
       </c>
       <c r="G100">
         <v>66</v>
@@ -9475,37 +9475,37 @@
         <v>2.17</v>
       </c>
       <c r="M100">
-        <v>53.78711184</v>
+        <v>54.33595992</v>
       </c>
       <c r="N100">
-        <v>-51.61711184</v>
+        <v>-52.16595992</v>
       </c>
       <c r="O100">
-        <v>-12.90427796</v>
+        <v>-13.04148998</v>
       </c>
       <c r="P100">
-        <v>-38.71283388</v>
+        <v>-39.12446994</v>
       </c>
       <c r="Q100">
-        <v>-37.57283388</v>
+        <v>-37.98446994</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.666671128750333</v>
+        <v>3.287542257500665</v>
       </c>
       <c r="T100">
-        <v>32.4881897715848</v>
+        <v>64.9763795431696</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0100860593075488</v>
+        <v>0.009984179920603858</v>
       </c>
       <c r="W100">
-        <v>0.23342170721528</v>
+        <v>0.2334457303747216</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.0403442372301952</v>
+        <v>0.03993671968241541</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2639866956459811</v>
-      </c>
-      <c r="C101">
-        <v>-139.4326872085018</v>
-      </c>
-      <c r="D101">
-        <v>24.99971279149819</v>
-      </c>
-      <c r="E101">
-        <v>229.3724</v>
-      </c>
-      <c r="F101">
-        <v>230.4324</v>
-      </c>
-      <c r="G101">
-        <v>66</v>
-      </c>
-      <c r="H101">
-        <v>231.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.31</v>
-      </c>
-      <c r="K101">
-        <v>1.14</v>
-      </c>
-      <c r="L101">
-        <v>2.17</v>
-      </c>
-      <c r="M101">
-        <v>54.33595992</v>
-      </c>
-      <c r="N101">
-        <v>-52.16595992</v>
-      </c>
-      <c r="O101">
-        <v>-13.04148998</v>
-      </c>
-      <c r="P101">
-        <v>-39.12446994</v>
-      </c>
-      <c r="Q101">
-        <v>-37.98446994</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.287542257500665</v>
-      </c>
-      <c r="T101">
-        <v>64.9763795431696</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.009984179920603858</v>
-      </c>
-      <c r="W101">
-        <v>0.2334457303747216</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.03993671968241541</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
